--- a/Data/Population/province.xlsx
+++ b/Data/Population/province.xlsx
@@ -20,6 +20,9 @@
     <t xml:space="preserve">Total</t>
   </si>
   <si>
+    <t xml:space="preserve">Bangkok</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chiang Mai</t>
   </si>
   <si>
@@ -59,6 +62,9 @@
     <t xml:space="preserve">Uttaradit</t>
   </si>
   <si>
+    <t xml:space="preserve">Chai Nat</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kamphaeng Phet</t>
   </si>
   <si>
@@ -71,12 +77,15 @@
     <t xml:space="preserve">Uthai Thani</t>
   </si>
   <si>
-    <t xml:space="preserve">Bangkok</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ang Thong</t>
   </si>
   <si>
+    <t xml:space="preserve">Lop Buri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nakhon Nayok</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nonthaburi</t>
   </si>
   <si>
@@ -86,12 +95,6 @@
     <t xml:space="preserve">Pathum Thani</t>
   </si>
   <si>
-    <t xml:space="preserve">Chai Nat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lop Buri</t>
-  </si>
-  <si>
     <t xml:space="preserve">Saraburi</t>
   </si>
   <si>
@@ -104,99 +107,99 @@
     <t xml:space="preserve">Nakhon Pathom</t>
   </si>
   <si>
+    <t xml:space="preserve">Phetchaburi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prachuap Khiri Khan</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ratchaburi</t>
   </si>
   <si>
+    <t xml:space="preserve">Samut Sakhon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samut Songkhram</t>
+  </si>
+  <si>
     <t xml:space="preserve">Suphan Buri</t>
   </si>
   <si>
-    <t xml:space="preserve">Phetchaburi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prachuap Khiri Khan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samut Sakhon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samut Songkhram</t>
-  </si>
-  <si>
     <t xml:space="preserve">Chachoengsao</t>
   </si>
   <si>
-    <t xml:space="preserve">Nakhon Nayok</t>
+    <t xml:space="preserve">Chanthaburi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chon Buri</t>
   </si>
   <si>
     <t xml:space="preserve">Prachin Buri</t>
   </si>
   <si>
+    <t xml:space="preserve">Rayong</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sa Kaeo</t>
   </si>
   <si>
     <t xml:space="preserve">Samut Prakan</t>
   </si>
   <si>
-    <t xml:space="preserve">Chanthaburi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chon Buri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rayong</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trat</t>
   </si>
   <si>
+    <t xml:space="preserve">Kalasin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khon Kaen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maha Sarakham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roi Et</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bungkan</t>
+  </si>
+  <si>
     <t xml:space="preserve">Loei</t>
   </si>
   <si>
+    <t xml:space="preserve">Nakhon Phanom</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nong Bua Lam Phu</t>
   </si>
   <si>
     <t xml:space="preserve">Nong Khai</t>
   </si>
   <si>
+    <t xml:space="preserve">Sakon Nakhon</t>
+  </si>
+  <si>
     <t xml:space="preserve">Udon Thani</t>
   </si>
   <si>
-    <t xml:space="preserve">Kalasin</t>
+    <t xml:space="preserve">Buri Ram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaiyaphum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nakhon Ratchasima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amnat Charoen</t>
   </si>
   <si>
     <t xml:space="preserve">Mukdahan</t>
   </si>
   <si>
-    <t xml:space="preserve">Nakhon Phanom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sakon Nakhon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khon Kaen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maha Sarakham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roi Et</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buri Ram</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chaiyaphum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nakhon Ratchasima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amnat Charoen</t>
-  </si>
-  <si>
     <t xml:space="preserve">Si Sa Ket</t>
   </si>
   <si>
@@ -209,46 +212,43 @@
     <t xml:space="preserve">Chumphon</t>
   </si>
   <si>
+    <t xml:space="preserve">Krabi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nakhon Si Thammarat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phangnga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phuket</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ranong</t>
   </si>
   <si>
     <t xml:space="preserve">Surat Thani</t>
   </si>
   <si>
-    <t xml:space="preserve">Nakhon Si Thammarat</t>
+    <t xml:space="preserve">Narathiwat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pattani</t>
   </si>
   <si>
     <t xml:space="preserve">Phatthalung</t>
   </si>
   <si>
+    <t xml:space="preserve">Satun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Songkhla</t>
+  </si>
+  <si>
     <t xml:space="preserve">Trang</t>
   </si>
   <si>
-    <t xml:space="preserve">Krabi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phangnga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phuket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narathiwat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pattani</t>
-  </si>
-  <si>
     <t xml:space="preserve">Yala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Satun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Songkhla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bungkan</t>
   </si>
 </sst>
 </file>
@@ -818,1293 +818,1295 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B2" t="n">
-        <v>62933515</v>
+        <v>63214022</v>
       </c>
       <c r="C2" t="n">
-        <v>1661349</v>
+        <v>5713566</v>
       </c>
       <c r="D2" t="n">
-        <v>1225364</v>
+        <v>1667358</v>
       </c>
       <c r="E2" t="n">
-        <v>772202</v>
+        <v>1226165</v>
       </c>
       <c r="F2" t="n">
-        <v>405361</v>
+        <v>769115</v>
       </c>
       <c r="G2" t="n">
-        <v>254990</v>
+        <v>405141</v>
       </c>
       <c r="H2" t="n">
-        <v>477522</v>
+        <v>253748</v>
       </c>
       <c r="I2" t="n">
-        <v>486399</v>
+        <v>476683</v>
       </c>
       <c r="J2" t="n">
-        <v>467125</v>
+        <v>486983</v>
       </c>
       <c r="K2" t="n">
-        <v>999924</v>
+        <v>464677</v>
       </c>
       <c r="L2" t="n">
-        <v>843096</v>
+        <v>996882</v>
       </c>
       <c r="M2" t="n">
-        <v>607061</v>
+        <v>842840</v>
       </c>
       <c r="N2" t="n">
-        <v>529303</v>
+        <v>604559</v>
       </c>
       <c r="O2" t="n">
-        <v>466380</v>
+        <v>534629</v>
       </c>
       <c r="P2" t="n">
-        <v>727158</v>
+        <v>464741</v>
       </c>
       <c r="Q2" t="n">
-        <v>1074849</v>
+        <v>336550</v>
       </c>
       <c r="R2" t="n">
-        <v>556287</v>
+        <v>726104</v>
       </c>
       <c r="S2" t="n">
-        <v>326982</v>
+        <v>1073962</v>
       </c>
       <c r="T2" t="n">
-        <v>5706103</v>
+        <v>554426</v>
       </c>
       <c r="U2" t="n">
-        <v>284175</v>
+        <v>327281</v>
       </c>
       <c r="V2" t="n">
-        <v>1011624</v>
+        <v>284619</v>
       </c>
       <c r="W2" t="n">
-        <v>757654</v>
+        <v>751811</v>
       </c>
       <c r="X2" t="n">
-        <v>879091</v>
+        <v>249625</v>
       </c>
       <c r="Y2" t="n">
-        <v>338077</v>
+        <v>1038392</v>
       </c>
       <c r="Z2" t="n">
-        <v>751298</v>
+        <v>764919</v>
       </c>
       <c r="AA2" t="n">
-        <v>612806</v>
+        <v>913047</v>
       </c>
       <c r="AB2" t="n">
-        <v>216311</v>
+        <v>618699</v>
       </c>
       <c r="AC2" t="n">
-        <v>834865</v>
+        <v>215602</v>
       </c>
       <c r="AD2" t="n">
-        <v>826438</v>
+        <v>838094</v>
       </c>
       <c r="AE2" t="n">
-        <v>830184</v>
+        <v>837285</v>
       </c>
       <c r="AF2" t="n">
-        <v>843245</v>
+        <v>457518</v>
       </c>
       <c r="AG2" t="n">
-        <v>456371</v>
+        <v>497483</v>
       </c>
       <c r="AH2" t="n">
-        <v>494502</v>
+        <v>833650</v>
       </c>
       <c r="AI2" t="n">
-        <v>466222</v>
+        <v>474041</v>
       </c>
       <c r="AJ2" t="n">
-        <v>194602</v>
+        <v>194134</v>
       </c>
       <c r="AK2" t="n">
-        <v>656586</v>
+        <v>843541</v>
       </c>
       <c r="AL2" t="n">
-        <v>249250</v>
+        <v>661898</v>
       </c>
       <c r="AM2" t="n">
-        <v>454404</v>
+        <v>506012</v>
       </c>
       <c r="AN2" t="n">
-        <v>538741</v>
+        <v>1249067</v>
       </c>
       <c r="AO2" t="n">
-        <v>1117284</v>
+        <v>457184</v>
       </c>
       <c r="AP2" t="n">
-        <v>503197</v>
+        <v>591067</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1221369</v>
+        <v>540281</v>
       </c>
       <c r="AR2" t="n">
-        <v>578628</v>
+        <v>1137082</v>
       </c>
       <c r="AS2" t="n">
-        <v>220246</v>
+        <v>221185</v>
       </c>
       <c r="AT2" t="n">
-        <v>614421</v>
+        <v>978046</v>
       </c>
       <c r="AU2" t="n">
-        <v>497148</v>
+        <v>1754258</v>
       </c>
       <c r="AV2" t="n">
-        <v>901100</v>
+        <v>936430</v>
       </c>
       <c r="AW2" t="n">
-        <v>1529124</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>976536</v>
-      </c>
+        <v>1307901</v>
+      </c>
+      <c r="AX2"/>
       <c r="AY2" t="n">
-        <v>335778</v>
+        <v>616981</v>
       </c>
       <c r="AZ2" t="n">
-        <v>696229</v>
+        <v>698235</v>
       </c>
       <c r="BA2" t="n">
-        <v>1111056</v>
+        <v>498562</v>
       </c>
       <c r="BB2" t="n">
-        <v>1751458</v>
+        <v>904748</v>
       </c>
       <c r="BC2" t="n">
-        <v>936846</v>
+        <v>1114550</v>
       </c>
       <c r="BD2" t="n">
-        <v>1309318</v>
+        <v>1533158</v>
       </c>
       <c r="BE2" t="n">
-        <v>1536396</v>
+        <v>1538861</v>
       </c>
       <c r="BF2" t="n">
-        <v>1119372</v>
+        <v>1121123</v>
       </c>
       <c r="BG2" t="n">
-        <v>2554241</v>
+        <v>2559006</v>
       </c>
       <c r="BH2" t="n">
-        <v>1373965</v>
+        <v>1374116</v>
       </c>
       <c r="BI2" t="n">
-        <v>368925</v>
+        <v>369196</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1444748</v>
+        <v>336802</v>
       </c>
       <c r="BK2" t="n">
-        <v>1784372</v>
+        <v>1442212</v>
       </c>
       <c r="BL2" t="n">
-        <v>540216</v>
+        <v>1790581</v>
       </c>
       <c r="BM2" t="n">
-        <v>480131</v>
+        <v>539414</v>
       </c>
       <c r="BN2" t="n">
-        <v>180319</v>
+        <v>483011</v>
       </c>
       <c r="BO2" t="n">
-        <v>965561</v>
+        <v>414670</v>
       </c>
       <c r="BP2" t="n">
-        <v>1508729</v>
+        <v>1510081</v>
       </c>
       <c r="BQ2" t="n">
-        <v>502943</v>
+        <v>248411</v>
       </c>
       <c r="BR2" t="n">
-        <v>608892</v>
+        <v>321252</v>
       </c>
       <c r="BS2" t="n">
-        <v>406999</v>
+        <v>181758</v>
       </c>
       <c r="BT2" t="n">
-        <v>246141</v>
+        <v>976956</v>
       </c>
       <c r="BU2" t="n">
-        <v>308118</v>
+        <v>715724</v>
       </c>
       <c r="BV2" t="n">
-        <v>709345</v>
+        <v>639988</v>
       </c>
       <c r="BW2" t="n">
-        <v>636768</v>
+        <v>503847</v>
       </c>
       <c r="BX2" t="n">
-        <v>469472</v>
+        <v>286446</v>
       </c>
       <c r="BY2" t="n">
-        <v>283014</v>
+        <v>1330342</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1321209</v>
-      </c>
-      <c r="CA2"/>
+        <v>612601</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>473109</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B3" t="n">
-        <v>63214022</v>
+        <v>63457439</v>
       </c>
       <c r="C3" t="n">
-        <v>1667358</v>
+        <v>5706739</v>
       </c>
       <c r="D3" t="n">
-        <v>1226165</v>
+        <v>1651433</v>
       </c>
       <c r="E3" t="n">
-        <v>769115</v>
+        <v>1211126</v>
       </c>
       <c r="F3" t="n">
-        <v>405141</v>
+        <v>766057</v>
       </c>
       <c r="G3" t="n">
-        <v>253748</v>
+        <v>404910</v>
       </c>
       <c r="H3" t="n">
-        <v>476683</v>
+        <v>247270</v>
       </c>
       <c r="I3" t="n">
-        <v>486983</v>
+        <v>475799</v>
       </c>
       <c r="J3" t="n">
-        <v>464677</v>
+        <v>487254</v>
       </c>
       <c r="K3" t="n">
-        <v>996882</v>
+        <v>462784</v>
       </c>
       <c r="L3" t="n">
-        <v>842840</v>
+        <v>995679</v>
       </c>
       <c r="M3" t="n">
-        <v>604559</v>
+        <v>844779</v>
       </c>
       <c r="N3" t="n">
-        <v>534629</v>
+        <v>603316</v>
       </c>
       <c r="O3" t="n">
-        <v>464741</v>
+        <v>528997</v>
       </c>
       <c r="P3" t="n">
-        <v>726104</v>
+        <v>463579</v>
       </c>
       <c r="Q3" t="n">
-        <v>1073962</v>
+        <v>335686</v>
       </c>
       <c r="R3" t="n">
-        <v>554426</v>
+        <v>726530</v>
       </c>
       <c r="S3" t="n">
-        <v>327281</v>
+        <v>1073554</v>
       </c>
       <c r="T3" t="n">
-        <v>5713566</v>
+        <v>553653</v>
       </c>
       <c r="U3" t="n">
-        <v>284619</v>
+        <v>327729</v>
       </c>
       <c r="V3" t="n">
-        <v>1038392</v>
+        <v>284819</v>
       </c>
       <c r="W3" t="n">
-        <v>764919</v>
+        <v>754127</v>
       </c>
       <c r="X3" t="n">
-        <v>913047</v>
+        <v>251219</v>
       </c>
       <c r="Y3" t="n">
-        <v>336550</v>
+        <v>1065332</v>
       </c>
       <c r="Z3" t="n">
-        <v>751811</v>
+        <v>772142</v>
       </c>
       <c r="AA3" t="n">
-        <v>618699</v>
+        <v>942813</v>
       </c>
       <c r="AB3" t="n">
-        <v>215602</v>
+        <v>617174</v>
       </c>
       <c r="AC3" t="n">
-        <v>838094</v>
+        <v>215426</v>
       </c>
       <c r="AD3" t="n">
-        <v>837285</v>
+        <v>837165</v>
       </c>
       <c r="AE3" t="n">
-        <v>833650</v>
+        <v>847513</v>
       </c>
       <c r="AF3" t="n">
-        <v>843541</v>
+        <v>460108</v>
       </c>
       <c r="AG3" t="n">
-        <v>457518</v>
+        <v>502221</v>
       </c>
       <c r="AH3" t="n">
-        <v>497483</v>
+        <v>835546</v>
       </c>
       <c r="AI3" t="n">
-        <v>474041</v>
+        <v>481377</v>
       </c>
       <c r="AJ3" t="n">
-        <v>194134</v>
+        <v>193851</v>
       </c>
       <c r="AK3" t="n">
-        <v>661898</v>
+        <v>844545</v>
       </c>
       <c r="AL3" t="n">
-        <v>249625</v>
+        <v>666907</v>
       </c>
       <c r="AM3" t="n">
-        <v>457184</v>
+        <v>509633</v>
       </c>
       <c r="AN3" t="n">
-        <v>540281</v>
+        <v>1277139</v>
       </c>
       <c r="AO3" t="n">
-        <v>1137082</v>
+        <v>460617</v>
       </c>
       <c r="AP3" t="n">
-        <v>506012</v>
+        <v>605380</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1249067</v>
+        <v>541939</v>
       </c>
       <c r="AR3" t="n">
-        <v>591067</v>
+        <v>1155665</v>
       </c>
       <c r="AS3" t="n">
-        <v>221185</v>
+        <v>220918</v>
       </c>
       <c r="AT3" t="n">
-        <v>616981</v>
+        <v>979371</v>
       </c>
       <c r="AU3" t="n">
-        <v>498562</v>
+        <v>1759172</v>
       </c>
       <c r="AV3" t="n">
-        <v>904748</v>
+        <v>937972</v>
       </c>
       <c r="AW3" t="n">
-        <v>1533158</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>978046</v>
-      </c>
+        <v>1307686</v>
+      </c>
+      <c r="AX3"/>
       <c r="AY3" t="n">
-        <v>336802</v>
+        <v>619602</v>
       </c>
       <c r="AZ3" t="n">
-        <v>698235</v>
+        <v>700027</v>
       </c>
       <c r="BA3" t="n">
-        <v>1114550</v>
+        <v>500217</v>
       </c>
       <c r="BB3" t="n">
-        <v>1754258</v>
+        <v>907064</v>
       </c>
       <c r="BC3" t="n">
-        <v>936430</v>
+        <v>1117242</v>
       </c>
       <c r="BD3" t="n">
-        <v>1307901</v>
+        <v>1537285</v>
       </c>
       <c r="BE3" t="n">
-        <v>1538861</v>
+        <v>1544218</v>
       </c>
       <c r="BF3" t="n">
-        <v>1121123</v>
+        <v>1123907</v>
       </c>
       <c r="BG3" t="n">
-        <v>2559006</v>
+        <v>2568205</v>
       </c>
       <c r="BH3" t="n">
-        <v>1374116</v>
+        <v>1376694</v>
       </c>
       <c r="BI3" t="n">
-        <v>369196</v>
+        <v>370141</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1442212</v>
+        <v>337773</v>
       </c>
       <c r="BK3" t="n">
-        <v>1790581</v>
+        <v>1443879</v>
       </c>
       <c r="BL3" t="n">
-        <v>539414</v>
+        <v>1799604</v>
       </c>
       <c r="BM3" t="n">
-        <v>483011</v>
+        <v>539210</v>
       </c>
       <c r="BN3" t="n">
-        <v>181758</v>
+        <v>486233</v>
       </c>
       <c r="BO3" t="n">
-        <v>976956</v>
+        <v>422631</v>
       </c>
       <c r="BP3" t="n">
-        <v>1510081</v>
+        <v>1514832</v>
       </c>
       <c r="BQ3" t="n">
-        <v>503847</v>
+        <v>250796</v>
       </c>
       <c r="BR3" t="n">
-        <v>612601</v>
+        <v>331460</v>
       </c>
       <c r="BS3" t="n">
-        <v>414670</v>
+        <v>182242</v>
       </c>
       <c r="BT3" t="n">
-        <v>248411</v>
+        <v>988854</v>
       </c>
       <c r="BU3" t="n">
-        <v>321252</v>
+        <v>724001</v>
       </c>
       <c r="BV3" t="n">
-        <v>715724</v>
+        <v>644897</v>
       </c>
       <c r="BW3" t="n">
-        <v>639988</v>
+        <v>506454</v>
       </c>
       <c r="BX3" t="n">
-        <v>473109</v>
+        <v>290755</v>
       </c>
       <c r="BY3" t="n">
-        <v>286446</v>
+        <v>1339861</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1330342</v>
-      </c>
-      <c r="CA3"/>
+        <v>616773</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>477931</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B4" t="n">
-        <v>63457439</v>
+        <v>63701703</v>
       </c>
       <c r="C4" t="n">
-        <v>1651433</v>
+        <v>5701995</v>
       </c>
       <c r="D4" t="n">
-        <v>1211126</v>
+        <v>1636514</v>
       </c>
       <c r="E4" t="n">
-        <v>766057</v>
+        <v>1196576</v>
       </c>
       <c r="F4" t="n">
-        <v>404910</v>
+        <v>763224</v>
       </c>
       <c r="G4" t="n">
-        <v>247270</v>
+        <v>404627</v>
       </c>
       <c r="H4" t="n">
-        <v>475799</v>
+        <v>242295</v>
       </c>
       <c r="I4" t="n">
-        <v>487254</v>
+        <v>475989</v>
       </c>
       <c r="J4" t="n">
-        <v>462784</v>
+        <v>486713</v>
       </c>
       <c r="K4" t="n">
-        <v>995679</v>
+        <v>461423</v>
       </c>
       <c r="L4" t="n">
-        <v>844779</v>
+        <v>995578</v>
       </c>
       <c r="M4" t="n">
-        <v>603316</v>
+        <v>847627</v>
       </c>
       <c r="N4" t="n">
-        <v>528997</v>
+        <v>602296</v>
       </c>
       <c r="O4" t="n">
-        <v>463579</v>
+        <v>522673</v>
       </c>
       <c r="P4" t="n">
-        <v>726530</v>
+        <v>462785</v>
       </c>
       <c r="Q4" t="n">
-        <v>1073554</v>
+        <v>335177</v>
       </c>
       <c r="R4" t="n">
-        <v>553653</v>
+        <v>726970</v>
       </c>
       <c r="S4" t="n">
-        <v>327729</v>
+        <v>1073182</v>
       </c>
       <c r="T4" t="n">
-        <v>5706739</v>
+        <v>552942</v>
       </c>
       <c r="U4" t="n">
-        <v>284819</v>
+        <v>327916</v>
       </c>
       <c r="V4" t="n">
-        <v>1065332</v>
+        <v>284889</v>
       </c>
       <c r="W4" t="n">
-        <v>772142</v>
+        <v>755153</v>
       </c>
       <c r="X4" t="n">
-        <v>942813</v>
+        <v>252209</v>
       </c>
       <c r="Y4" t="n">
-        <v>335686</v>
+        <v>1089908</v>
       </c>
       <c r="Z4" t="n">
-        <v>754127</v>
+        <v>778627</v>
       </c>
       <c r="AA4" t="n">
-        <v>617174</v>
+        <v>971010</v>
       </c>
       <c r="AB4" t="n">
-        <v>215426</v>
+        <v>615046</v>
       </c>
       <c r="AC4" t="n">
-        <v>837165</v>
+        <v>214981</v>
       </c>
       <c r="AD4" t="n">
-        <v>847513</v>
+        <v>836600</v>
       </c>
       <c r="AE4" t="n">
-        <v>835546</v>
+        <v>855837</v>
       </c>
       <c r="AF4" t="n">
-        <v>844545</v>
+        <v>462636</v>
       </c>
       <c r="AG4" t="n">
-        <v>460108</v>
+        <v>506599</v>
       </c>
       <c r="AH4" t="n">
-        <v>502221</v>
+        <v>837153</v>
       </c>
       <c r="AI4" t="n">
-        <v>481377</v>
+        <v>488247</v>
       </c>
       <c r="AJ4" t="n">
-        <v>193851</v>
+        <v>193853</v>
       </c>
       <c r="AK4" t="n">
-        <v>666907</v>
+        <v>845220</v>
       </c>
       <c r="AL4" t="n">
-        <v>251219</v>
+        <v>671458</v>
       </c>
       <c r="AM4" t="n">
-        <v>460617</v>
+        <v>512932</v>
       </c>
       <c r="AN4" t="n">
-        <v>541939</v>
+        <v>1302942</v>
       </c>
       <c r="AO4" t="n">
-        <v>1155665</v>
+        <v>464213</v>
       </c>
       <c r="AP4" t="n">
-        <v>509633</v>
+        <v>619249</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1277139</v>
+        <v>543276</v>
       </c>
       <c r="AR4" t="n">
-        <v>605380</v>
+        <v>1174643</v>
       </c>
       <c r="AS4" t="n">
-        <v>220918</v>
+        <v>220465</v>
       </c>
       <c r="AT4" t="n">
-        <v>619602</v>
+        <v>981369</v>
       </c>
       <c r="AU4" t="n">
-        <v>500217</v>
+        <v>1764922</v>
       </c>
       <c r="AV4" t="n">
-        <v>907064</v>
+        <v>940001</v>
       </c>
       <c r="AW4" t="n">
-        <v>1537285</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>979371</v>
-      </c>
+        <v>1308934</v>
+      </c>
+      <c r="AX4"/>
       <c r="AY4" t="n">
-        <v>337773</v>
+        <v>622424</v>
       </c>
       <c r="AZ4" t="n">
-        <v>700027</v>
+        <v>702041</v>
       </c>
       <c r="BA4" t="n">
-        <v>1117242</v>
+        <v>501891</v>
       </c>
       <c r="BB4" t="n">
-        <v>1759172</v>
+        <v>910094</v>
       </c>
       <c r="BC4" t="n">
-        <v>937972</v>
+        <v>1120678</v>
       </c>
       <c r="BD4" t="n">
-        <v>1307686</v>
+        <v>1541863</v>
       </c>
       <c r="BE4" t="n">
-        <v>1544218</v>
+        <v>1550275</v>
       </c>
       <c r="BF4" t="n">
-        <v>1123907</v>
+        <v>1126295</v>
       </c>
       <c r="BG4" t="n">
-        <v>2568205</v>
+        <v>2576691</v>
       </c>
       <c r="BH4" t="n">
-        <v>1376694</v>
+        <v>1379794</v>
       </c>
       <c r="BI4" t="n">
-        <v>370141</v>
+        <v>371471</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1443879</v>
+        <v>338812</v>
       </c>
       <c r="BK4" t="n">
-        <v>1799604</v>
+        <v>1449409</v>
       </c>
       <c r="BL4" t="n">
-        <v>539210</v>
+        <v>1808422</v>
       </c>
       <c r="BM4" t="n">
-        <v>486233</v>
+        <v>539196</v>
       </c>
       <c r="BN4" t="n">
-        <v>182242</v>
+        <v>488855</v>
       </c>
       <c r="BO4" t="n">
-        <v>988854</v>
+        <v>429631</v>
       </c>
       <c r="BP4" t="n">
-        <v>1514832</v>
+        <v>1519531</v>
       </c>
       <c r="BQ4" t="n">
-        <v>506454</v>
+        <v>252385</v>
       </c>
       <c r="BR4" t="n">
-        <v>616773</v>
+        <v>340490</v>
       </c>
       <c r="BS4" t="n">
-        <v>422631</v>
+        <v>182417</v>
       </c>
       <c r="BT4" t="n">
-        <v>250796</v>
+        <v>997302</v>
       </c>
       <c r="BU4" t="n">
-        <v>331460</v>
+        <v>732617</v>
       </c>
       <c r="BV4" t="n">
-        <v>724001</v>
+        <v>651442</v>
       </c>
       <c r="BW4" t="n">
-        <v>644897</v>
+        <v>508656</v>
       </c>
       <c r="BX4" t="n">
-        <v>477931</v>
+        <v>295133</v>
       </c>
       <c r="BY4" t="n">
-        <v>290755</v>
+        <v>1350489</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1339861</v>
-      </c>
-      <c r="CA4"/>
+        <v>620668</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>483857</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B5" t="n">
-        <v>63701703</v>
+        <v>63977185</v>
       </c>
       <c r="C5" t="n">
-        <v>1636514</v>
+        <v>5688119</v>
       </c>
       <c r="D5" t="n">
-        <v>1196576</v>
+        <v>1643312</v>
       </c>
       <c r="E5" t="n">
-        <v>763224</v>
+        <v>1198438</v>
       </c>
       <c r="F5" t="n">
-        <v>404627</v>
+        <v>759742</v>
       </c>
       <c r="G5" t="n">
-        <v>242295</v>
+        <v>404257</v>
       </c>
       <c r="H5" t="n">
-        <v>475989</v>
+        <v>243395</v>
       </c>
       <c r="I5" t="n">
-        <v>486713</v>
+        <v>476488</v>
       </c>
       <c r="J5" t="n">
-        <v>461423</v>
+        <v>486388</v>
       </c>
       <c r="K5" t="n">
-        <v>995578</v>
+        <v>459753</v>
       </c>
       <c r="L5" t="n">
-        <v>847627</v>
+        <v>993420</v>
       </c>
       <c r="M5" t="n">
-        <v>602296</v>
+        <v>850525</v>
       </c>
       <c r="N5" t="n">
-        <v>522673</v>
+        <v>601642</v>
       </c>
       <c r="O5" t="n">
-        <v>462785</v>
+        <v>528351</v>
       </c>
       <c r="P5" t="n">
-        <v>726970</v>
+        <v>461829</v>
       </c>
       <c r="Q5" t="n">
-        <v>1073182</v>
+        <v>334096</v>
       </c>
       <c r="R5" t="n">
-        <v>552942</v>
+        <v>726551</v>
       </c>
       <c r="S5" t="n">
-        <v>327916</v>
+        <v>1072591</v>
       </c>
       <c r="T5" t="n">
-        <v>5701995</v>
+        <v>551189</v>
       </c>
       <c r="U5" t="n">
-        <v>284889</v>
+        <v>327997</v>
       </c>
       <c r="V5" t="n">
-        <v>1089908</v>
+        <v>284516</v>
       </c>
       <c r="W5" t="n">
-        <v>778627</v>
+        <v>755991</v>
       </c>
       <c r="X5" t="n">
-        <v>971010</v>
+        <v>253283</v>
       </c>
       <c r="Y5" t="n">
-        <v>335177</v>
+        <v>1112185</v>
       </c>
       <c r="Z5" t="n">
-        <v>755153</v>
+        <v>784875</v>
       </c>
       <c r="AA5" t="n">
-        <v>615046</v>
+        <v>998271</v>
       </c>
       <c r="AB5" t="n">
-        <v>214981</v>
+        <v>618919</v>
       </c>
       <c r="AC5" t="n">
-        <v>836600</v>
+        <v>214124</v>
       </c>
       <c r="AD5" t="n">
-        <v>855837</v>
+        <v>839345</v>
       </c>
       <c r="AE5" t="n">
-        <v>837153</v>
+        <v>863155</v>
       </c>
       <c r="AF5" t="n">
-        <v>845220</v>
+        <v>465056</v>
       </c>
       <c r="AG5" t="n">
-        <v>462636</v>
+        <v>510852</v>
       </c>
       <c r="AH5" t="n">
-        <v>506599</v>
+        <v>840880</v>
       </c>
       <c r="AI5" t="n">
-        <v>488247</v>
+        <v>495493</v>
       </c>
       <c r="AJ5" t="n">
-        <v>193853</v>
+        <v>194072</v>
       </c>
       <c r="AK5" t="n">
-        <v>671458</v>
+        <v>845452</v>
       </c>
       <c r="AL5" t="n">
-        <v>252209</v>
+        <v>676652</v>
       </c>
       <c r="AM5" t="n">
-        <v>464213</v>
+        <v>515736</v>
       </c>
       <c r="AN5" t="n">
-        <v>543276</v>
+        <v>1327475</v>
       </c>
       <c r="AO5" t="n">
-        <v>1174643</v>
+        <v>468113</v>
       </c>
       <c r="AP5" t="n">
-        <v>512932</v>
+        <v>632069</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1302942</v>
+        <v>544848</v>
       </c>
       <c r="AR5" t="n">
-        <v>619249</v>
+        <v>1194202</v>
       </c>
       <c r="AS5" t="n">
-        <v>220465</v>
+        <v>221467</v>
       </c>
       <c r="AT5" t="n">
-        <v>622424</v>
+        <v>982117</v>
       </c>
       <c r="AU5" t="n">
-        <v>501891</v>
+        <v>1766834</v>
       </c>
       <c r="AV5" t="n">
-        <v>910094</v>
+        <v>940324</v>
       </c>
       <c r="AW5" t="n">
-        <v>1541863</v>
+        <v>1307384</v>
       </c>
       <c r="AX5" t="n">
-        <v>981369</v>
+        <v>203818</v>
       </c>
       <c r="AY5" t="n">
-        <v>338812</v>
+        <v>624493</v>
       </c>
       <c r="AZ5" t="n">
-        <v>702041</v>
+        <v>704080</v>
       </c>
       <c r="BA5" t="n">
-        <v>1120678</v>
+        <v>502710</v>
       </c>
       <c r="BB5" t="n">
-        <v>1764922</v>
+        <v>711404</v>
       </c>
       <c r="BC5" t="n">
-        <v>940001</v>
+        <v>1123129</v>
       </c>
       <c r="BD5" t="n">
-        <v>1308934</v>
+        <v>1546447</v>
       </c>
       <c r="BE5" t="n">
-        <v>1550275</v>
+        <v>1556426</v>
       </c>
       <c r="BF5" t="n">
-        <v>1126295</v>
+        <v>1127423</v>
       </c>
       <c r="BG5" t="n">
-        <v>2576691</v>
+        <v>2583707</v>
       </c>
       <c r="BH5" t="n">
-        <v>1379794</v>
+        <v>1381081</v>
       </c>
       <c r="BI5" t="n">
-        <v>371471</v>
+        <v>372190</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1449409</v>
+        <v>340079</v>
       </c>
       <c r="BK5" t="n">
-        <v>1808422</v>
+        <v>1452338</v>
       </c>
       <c r="BL5" t="n">
-        <v>539196</v>
+        <v>1814573</v>
       </c>
       <c r="BM5" t="n">
-        <v>488855</v>
+        <v>539055</v>
       </c>
       <c r="BN5" t="n">
-        <v>182417</v>
+        <v>491073</v>
       </c>
       <c r="BO5" t="n">
-        <v>997302</v>
+        <v>435372</v>
       </c>
       <c r="BP5" t="n">
-        <v>1519531</v>
+        <v>1524317</v>
       </c>
       <c r="BQ5" t="n">
-        <v>508656</v>
+        <v>254022</v>
       </c>
       <c r="BR5" t="n">
-        <v>620668</v>
+        <v>349457</v>
       </c>
       <c r="BS5" t="n">
-        <v>429631</v>
+        <v>183464</v>
       </c>
       <c r="BT5" t="n">
-        <v>252385</v>
+        <v>1006224</v>
       </c>
       <c r="BU5" t="n">
-        <v>340490</v>
+        <v>742268</v>
       </c>
       <c r="BV5" t="n">
-        <v>732617</v>
+        <v>659373</v>
       </c>
       <c r="BW5" t="n">
-        <v>651442</v>
+        <v>510299</v>
       </c>
       <c r="BX5" t="n">
-        <v>483857</v>
+        <v>299315</v>
       </c>
       <c r="BY5" t="n">
-        <v>295133</v>
+        <v>1362017</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1350489</v>
-      </c>
-      <c r="CA5"/>
+        <v>624684</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>490574</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B6" t="n">
-        <v>63977185</v>
+        <v>64075986</v>
       </c>
       <c r="C6" t="n">
-        <v>1643312</v>
+        <v>5674843</v>
       </c>
       <c r="D6" t="n">
-        <v>1198438</v>
+        <v>1646144</v>
       </c>
       <c r="E6" t="n">
-        <v>759742</v>
+        <v>1198656</v>
       </c>
       <c r="F6" t="n">
-        <v>404257</v>
+        <v>757534</v>
       </c>
       <c r="G6" t="n">
-        <v>243395</v>
+        <v>403952</v>
       </c>
       <c r="H6" t="n">
-        <v>476488</v>
+        <v>244048</v>
       </c>
       <c r="I6" t="n">
-        <v>486388</v>
+        <v>476612</v>
       </c>
       <c r="J6" t="n">
-        <v>459753</v>
+        <v>486472</v>
       </c>
       <c r="K6" t="n">
-        <v>993420</v>
+        <v>458750</v>
       </c>
       <c r="L6" t="n">
-        <v>850525</v>
+        <v>990807</v>
       </c>
       <c r="M6" t="n">
-        <v>601642</v>
+        <v>851357</v>
       </c>
       <c r="N6" t="n">
-        <v>528351</v>
+        <v>601504</v>
       </c>
       <c r="O6" t="n">
-        <v>461829</v>
+        <v>531018</v>
       </c>
       <c r="P6" t="n">
-        <v>726551</v>
+        <v>461040</v>
       </c>
       <c r="Q6" t="n">
-        <v>1072591</v>
+        <v>333256</v>
       </c>
       <c r="R6" t="n">
-        <v>551189</v>
+        <v>726009</v>
       </c>
       <c r="S6" t="n">
-        <v>327997</v>
+        <v>1071686</v>
       </c>
       <c r="T6" t="n">
-        <v>5688119</v>
+        <v>549688</v>
       </c>
       <c r="U6" t="n">
-        <v>284516</v>
+        <v>328034</v>
       </c>
       <c r="V6" t="n">
-        <v>1112185</v>
+        <v>284061</v>
       </c>
       <c r="W6" t="n">
-        <v>784875</v>
+        <v>756127</v>
       </c>
       <c r="X6" t="n">
-        <v>998271</v>
+        <v>253831</v>
       </c>
       <c r="Y6" t="n">
-        <v>334096</v>
+        <v>1122627</v>
       </c>
       <c r="Z6" t="n">
-        <v>755991</v>
+        <v>787653</v>
       </c>
       <c r="AA6" t="n">
-        <v>618919</v>
+        <v>1010898</v>
       </c>
       <c r="AB6" t="n">
-        <v>214124</v>
+        <v>620454</v>
       </c>
       <c r="AC6" t="n">
-        <v>839345</v>
+        <v>213587</v>
       </c>
       <c r="AD6" t="n">
-        <v>863155</v>
+        <v>838914</v>
       </c>
       <c r="AE6" t="n">
-        <v>840880</v>
+        <v>866064</v>
       </c>
       <c r="AF6" t="n">
-        <v>845452</v>
+        <v>466079</v>
       </c>
       <c r="AG6" t="n">
-        <v>465056</v>
+        <v>512568</v>
       </c>
       <c r="AH6" t="n">
-        <v>510852</v>
+        <v>842684</v>
       </c>
       <c r="AI6" t="n">
-        <v>495493</v>
+        <v>499098</v>
       </c>
       <c r="AJ6" t="n">
-        <v>194072</v>
+        <v>194086</v>
       </c>
       <c r="AK6" t="n">
-        <v>676652</v>
+        <v>845053</v>
       </c>
       <c r="AL6" t="n">
-        <v>253283</v>
+        <v>679370</v>
       </c>
       <c r="AM6" t="n">
-        <v>468113</v>
+        <v>516855</v>
       </c>
       <c r="AN6" t="n">
-        <v>544848</v>
+        <v>1338656</v>
       </c>
       <c r="AO6" t="n">
-        <v>1194202</v>
+        <v>469652</v>
       </c>
       <c r="AP6" t="n">
-        <v>515736</v>
+        <v>637736</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1327475</v>
+        <v>545596</v>
       </c>
       <c r="AR6" t="n">
-        <v>632069</v>
+        <v>1203223</v>
       </c>
       <c r="AS6" t="n">
-        <v>221467</v>
+        <v>222013</v>
       </c>
       <c r="AT6" t="n">
-        <v>624493</v>
+        <v>981655</v>
       </c>
       <c r="AU6" t="n">
-        <v>502710</v>
+        <v>1766066</v>
       </c>
       <c r="AV6" t="n">
-        <v>711404</v>
+        <v>939736</v>
       </c>
       <c r="AW6" t="n">
-        <v>1546447</v>
+        <v>1305058</v>
       </c>
       <c r="AX6" t="n">
-        <v>982117</v>
+        <v>407634</v>
       </c>
       <c r="AY6" t="n">
-        <v>340079</v>
+        <v>624920</v>
       </c>
       <c r="AZ6" t="n">
-        <v>704080</v>
+        <v>704768</v>
       </c>
       <c r="BA6" t="n">
-        <v>1123129</v>
+        <v>502551</v>
       </c>
       <c r="BB6" t="n">
-        <v>1766834</v>
+        <v>509870</v>
       </c>
       <c r="BC6" t="n">
-        <v>940324</v>
+        <v>1123351</v>
       </c>
       <c r="BD6" t="n">
-        <v>1307384</v>
+        <v>1548107</v>
       </c>
       <c r="BE6" t="n">
-        <v>1556426</v>
+        <v>1559085</v>
       </c>
       <c r="BF6" t="n">
         <v>1127423</v>
       </c>
       <c r="BG6" t="n">
-        <v>2583707</v>
+        <v>2585325</v>
       </c>
       <c r="BH6" t="n">
-        <v>1381081</v>
+        <v>1380399</v>
       </c>
       <c r="BI6" t="n">
-        <v>372190</v>
+        <v>372241</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1452338</v>
+        <v>340581</v>
       </c>
       <c r="BK6" t="n">
-        <v>1814573</v>
+        <v>1452203</v>
       </c>
       <c r="BL6" t="n">
-        <v>539055</v>
+        <v>1816057</v>
       </c>
       <c r="BM6" t="n">
-        <v>491073</v>
+        <v>538853</v>
       </c>
       <c r="BN6" t="n">
-        <v>183464</v>
+        <v>492182</v>
       </c>
       <c r="BO6" t="n">
-        <v>1006224</v>
+        <v>438039</v>
       </c>
       <c r="BP6" t="n">
-        <v>1524317</v>
+        <v>1526071</v>
       </c>
       <c r="BQ6" t="n">
-        <v>510299</v>
+        <v>254931</v>
       </c>
       <c r="BR6" t="n">
-        <v>624684</v>
+        <v>353847</v>
       </c>
       <c r="BS6" t="n">
-        <v>435372</v>
+        <v>183849</v>
       </c>
       <c r="BT6" t="n">
-        <v>254022</v>
+        <v>1012064</v>
       </c>
       <c r="BU6" t="n">
-        <v>349457</v>
+        <v>747372</v>
       </c>
       <c r="BV6" t="n">
-        <v>742268</v>
+        <v>663485</v>
       </c>
       <c r="BW6" t="n">
-        <v>659373</v>
+        <v>511016</v>
       </c>
       <c r="BX6" t="n">
-        <v>490574</v>
+        <v>301467</v>
       </c>
       <c r="BY6" t="n">
-        <v>299315</v>
+        <v>1367010</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1362017</v>
+        <v>626708</v>
       </c>
       <c r="CA6" t="n">
-        <v>203818</v>
+        <v>493767</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B7" t="n">
-        <v>64075986</v>
+        <v>64076033</v>
       </c>
       <c r="C7" t="n">
+        <v>5674843</v>
+      </c>
+      <c r="D7" t="n">
         <v>1646144</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>1198656</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>757534</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>403952</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>244048</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>476612</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>486472</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>458750</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>990807</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>851357</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>601504</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>531018</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>461040</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
+        <v>333256</v>
+      </c>
+      <c r="R7" t="n">
         <v>726009</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>1071686</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>549688</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>328034</v>
       </c>
-      <c r="T7" t="n">
-        <v>5674843</v>
-      </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>284061</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
+        <v>756127</v>
+      </c>
+      <c r="X7" t="n">
+        <v>253831</v>
+      </c>
+      <c r="Y7" t="n">
         <v>1122627</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Z7" t="n">
         <v>787653</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AA7" t="n">
         <v>1010898</v>
       </c>
-      <c r="Y7" t="n">
-        <v>333256</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>756127</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
         <v>620454</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>213587</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>838914</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AE7" t="n">
         <v>866064</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AF7" t="n">
+        <v>466079</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>512568</v>
+      </c>
+      <c r="AH7" t="n">
         <v>842684</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>845053</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>466079</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>512568</v>
       </c>
       <c r="AI7" t="n">
         <v>499098</v>
@@ -2113,64 +2115,64 @@
         <v>194086</v>
       </c>
       <c r="AK7" t="n">
+        <v>845053</v>
+      </c>
+      <c r="AL7" t="n">
         <v>679370</v>
       </c>
-      <c r="AL7" t="n">
-        <v>253831</v>
-      </c>
       <c r="AM7" t="n">
+        <v>516855</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1338656</v>
+      </c>
+      <c r="AO7" t="n">
         <v>469652</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AP7" t="n">
+        <v>637736</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>545596</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AR7" t="n">
         <v>1203223</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>516855</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1338656</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>637736</v>
       </c>
       <c r="AS7" t="n">
         <v>222013</v>
       </c>
       <c r="AT7" t="n">
+        <v>981655</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1766066</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>939736</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1305058</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>407634</v>
+      </c>
+      <c r="AY7" t="n">
         <v>624920</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>502551</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>509870</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1548107</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>981655</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>340581</v>
       </c>
       <c r="AZ7" t="n">
         <v>704768</v>
       </c>
       <c r="BA7" t="n">
+        <v>502551</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>509870</v>
+      </c>
+      <c r="BC7" t="n">
         <v>1123351</v>
       </c>
-      <c r="BB7" t="n">
-        <v>1766066</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>939736</v>
-      </c>
       <c r="BD7" t="n">
-        <v>1305058</v>
+        <v>1548107</v>
       </c>
       <c r="BE7" t="n">
         <v>1559085</v>
@@ -2188,2687 +2190,2687 @@
         <v>372241</v>
       </c>
       <c r="BJ7" t="n">
+        <v>340581</v>
+      </c>
+      <c r="BK7" t="n">
         <v>1452203</v>
       </c>
-      <c r="BK7" t="n">
+      <c r="BL7" t="n">
         <v>1816057</v>
       </c>
-      <c r="BL7" t="n">
+      <c r="BM7" t="n">
         <v>538853</v>
       </c>
-      <c r="BM7" t="n">
+      <c r="BN7" t="n">
         <v>492182</v>
       </c>
-      <c r="BN7" t="n">
-        <v>183849</v>
-      </c>
       <c r="BO7" t="n">
-        <v>1012064</v>
+        <v>438039</v>
       </c>
       <c r="BP7" t="n">
         <v>1526071</v>
       </c>
       <c r="BQ7" t="n">
-        <v>511016</v>
+        <v>254931</v>
       </c>
       <c r="BR7" t="n">
+        <v>353847</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>183849</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1012064</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>747372</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>663485</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>511063</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>301467</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1367010</v>
+      </c>
+      <c r="BZ7" t="n">
         <v>626708</v>
       </c>
-      <c r="BS7" t="n">
-        <v>438039</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>254931</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>353847</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>747372</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>663485</v>
-      </c>
-      <c r="BX7" t="n">
+      <c r="CA7" t="n">
         <v>493767</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>301467</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1367010</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>407634</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B8" t="n">
-        <v>64076033</v>
+        <v>64955313</v>
       </c>
       <c r="C8" t="n">
-        <v>1646144</v>
+        <v>5689268</v>
       </c>
       <c r="D8" t="n">
-        <v>1198656</v>
+        <v>1672586</v>
       </c>
       <c r="E8" t="n">
-        <v>757534</v>
+        <v>1206180</v>
       </c>
       <c r="F8" t="n">
-        <v>403952</v>
+        <v>753937</v>
       </c>
       <c r="G8" t="n">
-        <v>244048</v>
+        <v>405368</v>
       </c>
       <c r="H8" t="n">
-        <v>476612</v>
+        <v>247364</v>
       </c>
       <c r="I8" t="n">
-        <v>486472</v>
+        <v>478088</v>
       </c>
       <c r="J8" t="n">
-        <v>458750</v>
+        <v>485599</v>
       </c>
       <c r="K8" t="n">
-        <v>990807</v>
+        <v>455078</v>
       </c>
       <c r="L8" t="n">
-        <v>851357</v>
+        <v>995102</v>
       </c>
       <c r="M8" t="n">
-        <v>601504</v>
+        <v>857682</v>
       </c>
       <c r="N8" t="n">
-        <v>531018</v>
+        <v>602586</v>
       </c>
       <c r="O8" t="n">
-        <v>461040</v>
+        <v>535953</v>
       </c>
       <c r="P8" t="n">
-        <v>726009</v>
+        <v>460698</v>
       </c>
       <c r="Q8" t="n">
-        <v>1071686</v>
+        <v>332526</v>
       </c>
       <c r="R8" t="n">
-        <v>549688</v>
+        <v>729076</v>
       </c>
       <c r="S8" t="n">
-        <v>328034</v>
+        <v>1072949</v>
       </c>
       <c r="T8" t="n">
-        <v>5674843</v>
+        <v>548199</v>
       </c>
       <c r="U8" t="n">
-        <v>284061</v>
+        <v>329858</v>
       </c>
       <c r="V8" t="n">
-        <v>1122627</v>
+        <v>283650</v>
       </c>
       <c r="W8" t="n">
-        <v>787653</v>
+        <v>758188</v>
       </c>
       <c r="X8" t="n">
-        <v>1010898</v>
+        <v>256693</v>
       </c>
       <c r="Y8" t="n">
-        <v>333256</v>
+        <v>1165070</v>
       </c>
       <c r="Z8" t="n">
-        <v>756127</v>
+        <v>800785</v>
       </c>
       <c r="AA8" t="n">
-        <v>620454</v>
+        <v>1063608</v>
       </c>
       <c r="AB8" t="n">
-        <v>213587</v>
+        <v>631338</v>
       </c>
       <c r="AC8" t="n">
-        <v>838914</v>
+        <v>212424</v>
       </c>
       <c r="AD8" t="n">
-        <v>866064</v>
+        <v>845540</v>
       </c>
       <c r="AE8" t="n">
-        <v>842684</v>
+        <v>886627</v>
       </c>
       <c r="AF8" t="n">
-        <v>845053</v>
+        <v>472640</v>
       </c>
       <c r="AG8" t="n">
-        <v>466079</v>
+        <v>522689</v>
       </c>
       <c r="AH8" t="n">
-        <v>512568</v>
+        <v>851689</v>
       </c>
       <c r="AI8" t="n">
-        <v>499098</v>
+        <v>525672</v>
       </c>
       <c r="AJ8" t="n">
-        <v>194086</v>
+        <v>194153</v>
       </c>
       <c r="AK8" t="n">
-        <v>679370</v>
+        <v>848559</v>
       </c>
       <c r="AL8" t="n">
-        <v>253831</v>
+        <v>692852</v>
       </c>
       <c r="AM8" t="n">
-        <v>469652</v>
+        <v>525805</v>
       </c>
       <c r="AN8" t="n">
-        <v>545596</v>
+        <v>1405889</v>
       </c>
       <c r="AO8" t="n">
-        <v>1203223</v>
+        <v>477741</v>
       </c>
       <c r="AP8" t="n">
-        <v>516855</v>
+        <v>667806</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1338656</v>
+        <v>551562</v>
       </c>
       <c r="AR8" t="n">
-        <v>637736</v>
+        <v>1251570</v>
       </c>
       <c r="AS8" t="n">
-        <v>222013</v>
+        <v>224370</v>
       </c>
       <c r="AT8" t="n">
-        <v>624920</v>
+        <v>984468</v>
       </c>
       <c r="AU8" t="n">
-        <v>502551</v>
+        <v>1785852</v>
       </c>
       <c r="AV8" t="n">
-        <v>509870</v>
+        <v>958116</v>
       </c>
       <c r="AW8" t="n">
-        <v>1548107</v>
+        <v>1308638</v>
       </c>
       <c r="AX8" t="n">
-        <v>981655</v>
+        <v>417401</v>
       </c>
       <c r="AY8" t="n">
-        <v>340581</v>
+        <v>633359</v>
       </c>
       <c r="AZ8" t="n">
-        <v>704768</v>
+        <v>712101</v>
       </c>
       <c r="BA8" t="n">
-        <v>1123351</v>
+        <v>508001</v>
       </c>
       <c r="BB8" t="n">
-        <v>1766066</v>
+        <v>516101</v>
       </c>
       <c r="BC8" t="n">
-        <v>939736</v>
+        <v>1136466</v>
       </c>
       <c r="BD8" t="n">
-        <v>1305058</v>
+        <v>1567132</v>
       </c>
       <c r="BE8" t="n">
-        <v>1559085</v>
+        <v>1576343</v>
       </c>
       <c r="BF8" t="n">
-        <v>1127423</v>
+        <v>1136386</v>
       </c>
       <c r="BG8" t="n">
-        <v>2585325</v>
+        <v>2615340</v>
       </c>
       <c r="BH8" t="n">
-        <v>1380399</v>
+        <v>1389915</v>
       </c>
       <c r="BI8" t="n">
-        <v>372241</v>
+        <v>375039</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1452203</v>
+        <v>345159</v>
       </c>
       <c r="BK8" t="n">
-        <v>1816057</v>
+        <v>1463620</v>
       </c>
       <c r="BL8" t="n">
-        <v>538853</v>
+        <v>1840596</v>
       </c>
       <c r="BM8" t="n">
-        <v>492182</v>
+        <v>540297</v>
       </c>
       <c r="BN8" t="n">
-        <v>183849</v>
+        <v>499435</v>
       </c>
       <c r="BO8" t="n">
-        <v>1012064</v>
+        <v>453850</v>
       </c>
       <c r="BP8" t="n">
-        <v>1526071</v>
+        <v>1544936</v>
       </c>
       <c r="BQ8" t="n">
-        <v>511063</v>
+        <v>260395</v>
       </c>
       <c r="BR8" t="n">
-        <v>626708</v>
+        <v>373943</v>
       </c>
       <c r="BS8" t="n">
-        <v>438039</v>
+        <v>175933</v>
       </c>
       <c r="BT8" t="n">
-        <v>254931</v>
+        <v>1036021</v>
       </c>
       <c r="BU8" t="n">
-        <v>353847</v>
+        <v>770472</v>
       </c>
       <c r="BV8" t="n">
-        <v>747372</v>
+        <v>682512</v>
       </c>
       <c r="BW8" t="n">
-        <v>663485</v>
+        <v>519220</v>
       </c>
       <c r="BX8" t="n">
-        <v>493767</v>
+        <v>311233</v>
       </c>
       <c r="BY8" t="n">
-        <v>301467</v>
+        <v>1395596</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1367010</v>
+        <v>637395</v>
       </c>
       <c r="CA8" t="n">
-        <v>407634</v>
+        <v>509025</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B9" t="n">
-        <v>64955313</v>
+        <v>65124716</v>
       </c>
       <c r="C9" t="n">
-        <v>1672586</v>
+        <v>5692284</v>
       </c>
       <c r="D9" t="n">
-        <v>1206180</v>
+        <v>1678284</v>
       </c>
       <c r="E9" t="n">
-        <v>753937</v>
+        <v>1207699</v>
       </c>
       <c r="F9" t="n">
-        <v>405368</v>
+        <v>753013</v>
       </c>
       <c r="G9" t="n">
-        <v>247364</v>
+        <v>405468</v>
       </c>
       <c r="H9" t="n">
-        <v>478088</v>
+        <v>248178</v>
       </c>
       <c r="I9" t="n">
-        <v>485599</v>
+        <v>478264</v>
       </c>
       <c r="J9" t="n">
-        <v>455078</v>
+        <v>484454</v>
       </c>
       <c r="K9" t="n">
-        <v>995102</v>
+        <v>454083</v>
       </c>
       <c r="L9" t="n">
-        <v>857682</v>
+        <v>995807</v>
       </c>
       <c r="M9" t="n">
-        <v>602586</v>
+        <v>858988</v>
       </c>
       <c r="N9" t="n">
-        <v>535953</v>
+        <v>602460</v>
       </c>
       <c r="O9" t="n">
-        <v>460698</v>
+        <v>539553</v>
       </c>
       <c r="P9" t="n">
-        <v>729076</v>
+        <v>460400</v>
       </c>
       <c r="Q9" t="n">
-        <v>1072949</v>
+        <v>332283</v>
       </c>
       <c r="R9" t="n">
-        <v>548199</v>
+        <v>729522</v>
       </c>
       <c r="S9" t="n">
-        <v>329858</v>
+        <v>1072756</v>
       </c>
       <c r="T9" t="n">
-        <v>5689268</v>
+        <v>547543</v>
       </c>
       <c r="U9" t="n">
-        <v>283650</v>
+        <v>330179</v>
       </c>
       <c r="V9" t="n">
-        <v>1165070</v>
+        <v>283568</v>
       </c>
       <c r="W9" t="n">
-        <v>800785</v>
+        <v>758406</v>
       </c>
       <c r="X9" t="n">
-        <v>1063608</v>
+        <v>257300</v>
       </c>
       <c r="Y9" t="n">
-        <v>332526</v>
+        <v>1173870</v>
       </c>
       <c r="Z9" t="n">
-        <v>758188</v>
+        <v>803599</v>
       </c>
       <c r="AA9" t="n">
-        <v>631338</v>
+        <v>1074058</v>
       </c>
       <c r="AB9" t="n">
-        <v>212424</v>
+        <v>633460</v>
       </c>
       <c r="AC9" t="n">
-        <v>845540</v>
+        <v>212158</v>
       </c>
       <c r="AD9" t="n">
-        <v>886627</v>
+        <v>848198</v>
       </c>
       <c r="AE9" t="n">
-        <v>851689</v>
+        <v>891071</v>
       </c>
       <c r="AF9" t="n">
-        <v>848559</v>
+        <v>474192</v>
       </c>
       <c r="AG9" t="n">
-        <v>472640</v>
+        <v>525107</v>
       </c>
       <c r="AH9" t="n">
-        <v>522689</v>
+        <v>853217</v>
       </c>
       <c r="AI9" t="n">
-        <v>525672</v>
+        <v>531887</v>
       </c>
       <c r="AJ9" t="n">
-        <v>194153</v>
+        <v>194189</v>
       </c>
       <c r="AK9" t="n">
-        <v>692852</v>
+        <v>849053</v>
       </c>
       <c r="AL9" t="n">
-        <v>256693</v>
+        <v>695478</v>
       </c>
       <c r="AM9" t="n">
-        <v>477741</v>
+        <v>527350</v>
       </c>
       <c r="AN9" t="n">
-        <v>551562</v>
+        <v>1421425</v>
       </c>
       <c r="AO9" t="n">
-        <v>1251570</v>
+        <v>479314</v>
       </c>
       <c r="AP9" t="n">
-        <v>525805</v>
+        <v>674393</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1405889</v>
+        <v>552187</v>
       </c>
       <c r="AR9" t="n">
-        <v>667806</v>
+        <v>1261530</v>
       </c>
       <c r="AS9" t="n">
-        <v>224370</v>
+        <v>224730</v>
       </c>
       <c r="AT9" t="n">
-        <v>633359</v>
+        <v>984907</v>
       </c>
       <c r="AU9" t="n">
-        <v>508001</v>
+        <v>1790049</v>
       </c>
       <c r="AV9" t="n">
-        <v>516101</v>
+        <v>960588</v>
       </c>
       <c r="AW9" t="n">
-        <v>1567132</v>
+        <v>1308318</v>
       </c>
       <c r="AX9" t="n">
-        <v>984468</v>
+        <v>418566</v>
       </c>
       <c r="AY9" t="n">
-        <v>345159</v>
+        <v>634513</v>
       </c>
       <c r="AZ9" t="n">
-        <v>712101</v>
+        <v>713341</v>
       </c>
       <c r="BA9" t="n">
-        <v>1136466</v>
+        <v>508864</v>
       </c>
       <c r="BB9" t="n">
-        <v>1785852</v>
+        <v>517260</v>
       </c>
       <c r="BC9" t="n">
-        <v>958116</v>
+        <v>1138609</v>
       </c>
       <c r="BD9" t="n">
-        <v>1308638</v>
+        <v>1570300</v>
       </c>
       <c r="BE9" t="n">
-        <v>1576343</v>
+        <v>1579248</v>
       </c>
       <c r="BF9" t="n">
-        <v>1136386</v>
+        <v>1137049</v>
       </c>
       <c r="BG9" t="n">
-        <v>2615340</v>
+        <v>2620517</v>
       </c>
       <c r="BH9" t="n">
-        <v>1389915</v>
+        <v>1391636</v>
       </c>
       <c r="BI9" t="n">
-        <v>375039</v>
+        <v>375380</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1463620</v>
+        <v>346016</v>
       </c>
       <c r="BK9" t="n">
-        <v>1840596</v>
+        <v>1465213</v>
       </c>
       <c r="BL9" t="n">
-        <v>540297</v>
+        <v>1844669</v>
       </c>
       <c r="BM9" t="n">
-        <v>499435</v>
+        <v>540211</v>
       </c>
       <c r="BN9" t="n">
-        <v>175933</v>
+        <v>500575</v>
       </c>
       <c r="BO9" t="n">
-        <v>1036021</v>
+        <v>456811</v>
       </c>
       <c r="BP9" t="n">
-        <v>1544936</v>
+        <v>1548028</v>
       </c>
       <c r="BQ9" t="n">
-        <v>519220</v>
+        <v>261370</v>
       </c>
       <c r="BR9" t="n">
-        <v>637395</v>
+        <v>378364</v>
       </c>
       <c r="BS9" t="n">
-        <v>453850</v>
+        <v>177089</v>
       </c>
       <c r="BT9" t="n">
-        <v>260395</v>
+        <v>1040230</v>
       </c>
       <c r="BU9" t="n">
-        <v>373943</v>
+        <v>774799</v>
       </c>
       <c r="BV9" t="n">
-        <v>770472</v>
+        <v>686186</v>
       </c>
       <c r="BW9" t="n">
-        <v>682512</v>
+        <v>520419</v>
       </c>
       <c r="BX9" t="n">
-        <v>509025</v>
+        <v>312673</v>
       </c>
       <c r="BY9" t="n">
-        <v>311233</v>
+        <v>1401303</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1395596</v>
+        <v>638746</v>
       </c>
       <c r="CA9" t="n">
-        <v>417401</v>
+        <v>511911</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B10" t="n">
-        <v>65124716</v>
+        <v>65426907</v>
       </c>
       <c r="C10" t="n">
-        <v>1678284</v>
+        <v>5694347</v>
       </c>
       <c r="D10" t="n">
-        <v>1207699</v>
+        <v>1703263</v>
       </c>
       <c r="E10" t="n">
-        <v>753013</v>
+        <v>1242825</v>
       </c>
       <c r="F10" t="n">
-        <v>405468</v>
+        <v>752685</v>
       </c>
       <c r="G10" t="n">
-        <v>248178</v>
+        <v>405927</v>
       </c>
       <c r="H10" t="n">
-        <v>478264</v>
+        <v>260971</v>
       </c>
       <c r="I10" t="n">
-        <v>484454</v>
+        <v>478890</v>
       </c>
       <c r="J10" t="n">
-        <v>454083</v>
+        <v>483550</v>
       </c>
       <c r="K10" t="n">
-        <v>995807</v>
+        <v>453213</v>
       </c>
       <c r="L10" t="n">
-        <v>858988</v>
+        <v>996397</v>
       </c>
       <c r="M10" t="n">
-        <v>602460</v>
+        <v>861194</v>
       </c>
       <c r="N10" t="n">
-        <v>539553</v>
+        <v>602085</v>
       </c>
       <c r="O10" t="n">
-        <v>460400</v>
+        <v>578968</v>
       </c>
       <c r="P10" t="n">
-        <v>729522</v>
+        <v>460084</v>
       </c>
       <c r="Q10" t="n">
-        <v>1072756</v>
+        <v>331968</v>
       </c>
       <c r="R10" t="n">
-        <v>547543</v>
+        <v>729839</v>
       </c>
       <c r="S10" t="n">
-        <v>330179</v>
+        <v>1072349</v>
       </c>
       <c r="T10" t="n">
-        <v>5692284</v>
+        <v>546750</v>
       </c>
       <c r="U10" t="n">
-        <v>283568</v>
+        <v>330543</v>
       </c>
       <c r="V10" t="n">
-        <v>1173870</v>
+        <v>283371</v>
       </c>
       <c r="W10" t="n">
-        <v>803599</v>
+        <v>758531</v>
       </c>
       <c r="X10" t="n">
-        <v>1074058</v>
+        <v>257939</v>
       </c>
       <c r="Y10" t="n">
-        <v>332283</v>
+        <v>1183791</v>
       </c>
       <c r="Z10" t="n">
-        <v>758406</v>
+        <v>805980</v>
       </c>
       <c r="AA10" t="n">
-        <v>633460</v>
+        <v>1084154</v>
       </c>
       <c r="AB10" t="n">
-        <v>212158</v>
+        <v>635567</v>
       </c>
       <c r="AC10" t="n">
-        <v>848198</v>
+        <v>211792</v>
       </c>
       <c r="AD10" t="n">
-        <v>891071</v>
+        <v>865172</v>
       </c>
       <c r="AE10" t="n">
-        <v>853217</v>
+        <v>895207</v>
       </c>
       <c r="AF10" t="n">
-        <v>849053</v>
+        <v>476391</v>
       </c>
       <c r="AG10" t="n">
-        <v>474192</v>
+        <v>529912</v>
       </c>
       <c r="AH10" t="n">
-        <v>525107</v>
+        <v>860549</v>
       </c>
       <c r="AI10" t="n">
-        <v>531887</v>
+        <v>538671</v>
       </c>
       <c r="AJ10" t="n">
-        <v>194189</v>
+        <v>194283</v>
       </c>
       <c r="AK10" t="n">
-        <v>695478</v>
+        <v>849376</v>
       </c>
       <c r="AL10" t="n">
-        <v>257300</v>
+        <v>698190</v>
       </c>
       <c r="AM10" t="n">
-        <v>479314</v>
+        <v>529194</v>
       </c>
       <c r="AN10" t="n">
-        <v>552187</v>
+        <v>1438231</v>
       </c>
       <c r="AO10" t="n">
-        <v>1261530</v>
+        <v>480755</v>
       </c>
       <c r="AP10" t="n">
-        <v>527350</v>
+        <v>681696</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1421425</v>
+        <v>554555</v>
       </c>
       <c r="AR10" t="n">
-        <v>674393</v>
+        <v>1270420</v>
       </c>
       <c r="AS10" t="n">
-        <v>224730</v>
+        <v>227083</v>
       </c>
       <c r="AT10" t="n">
-        <v>634513</v>
+        <v>985055</v>
       </c>
       <c r="AU10" t="n">
-        <v>508864</v>
+        <v>1794032</v>
       </c>
       <c r="AV10" t="n">
-        <v>517260</v>
+        <v>962592</v>
       </c>
       <c r="AW10" t="n">
-        <v>1570300</v>
+        <v>1308241</v>
       </c>
       <c r="AX10" t="n">
-        <v>984907</v>
+        <v>419607</v>
       </c>
       <c r="AY10" t="n">
-        <v>346016</v>
+        <v>636666</v>
       </c>
       <c r="AZ10" t="n">
-        <v>713341</v>
+        <v>714369</v>
       </c>
       <c r="BA10" t="n">
-        <v>1138609</v>
+        <v>509469</v>
       </c>
       <c r="BB10" t="n">
-        <v>1790049</v>
+        <v>518420</v>
       </c>
       <c r="BC10" t="n">
-        <v>960588</v>
+        <v>1140673</v>
       </c>
       <c r="BD10" t="n">
-        <v>1308318</v>
+        <v>1572726</v>
       </c>
       <c r="BE10" t="n">
-        <v>1579248</v>
+        <v>1581955</v>
       </c>
       <c r="BF10" t="n">
-        <v>1137049</v>
+        <v>1137651</v>
       </c>
       <c r="BG10" t="n">
-        <v>2620517</v>
+        <v>2624668</v>
       </c>
       <c r="BH10" t="n">
-        <v>1391636</v>
+        <v>1393330</v>
       </c>
       <c r="BI10" t="n">
-        <v>375380</v>
+        <v>375881</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1465213</v>
+        <v>347059</v>
       </c>
       <c r="BK10" t="n">
-        <v>1844669</v>
+        <v>1467006</v>
       </c>
       <c r="BL10" t="n">
-        <v>540211</v>
+        <v>1851049</v>
       </c>
       <c r="BM10" t="n">
-        <v>500575</v>
+        <v>540197</v>
       </c>
       <c r="BN10" t="n">
-        <v>177089</v>
+        <v>503203</v>
       </c>
       <c r="BO10" t="n">
-        <v>1040230</v>
+        <v>459456</v>
       </c>
       <c r="BP10" t="n">
-        <v>1548028</v>
+        <v>1550278</v>
       </c>
       <c r="BQ10" t="n">
-        <v>520419</v>
+        <v>262721</v>
       </c>
       <c r="BR10" t="n">
-        <v>638746</v>
+        <v>382485</v>
       </c>
       <c r="BS10" t="n">
-        <v>456811</v>
+        <v>182313</v>
       </c>
       <c r="BT10" t="n">
-        <v>261370</v>
+        <v>1043501</v>
       </c>
       <c r="BU10" t="n">
-        <v>378364</v>
+        <v>778941</v>
       </c>
       <c r="BV10" t="n">
-        <v>774799</v>
+        <v>690104</v>
       </c>
       <c r="BW10" t="n">
-        <v>686186</v>
+        <v>521570</v>
       </c>
       <c r="BX10" t="n">
-        <v>511911</v>
+        <v>314297</v>
       </c>
       <c r="BY10" t="n">
-        <v>312673</v>
+        <v>1405939</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1401303</v>
+        <v>639770</v>
       </c>
       <c r="CA10" t="n">
-        <v>418566</v>
+        <v>515025</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B11" t="n">
-        <v>65426907</v>
+        <v>66060027</v>
       </c>
       <c r="C11" t="n">
-        <v>1703263</v>
+        <v>5684531</v>
       </c>
       <c r="D11" t="n">
-        <v>1242825</v>
+        <v>1741301</v>
       </c>
       <c r="E11" t="n">
-        <v>752685</v>
+        <v>1285080</v>
       </c>
       <c r="F11" t="n">
-        <v>405927</v>
+        <v>747699</v>
       </c>
       <c r="G11" t="n">
-        <v>260971</v>
+        <v>405959</v>
       </c>
       <c r="H11" t="n">
-        <v>478890</v>
+        <v>277486</v>
       </c>
       <c r="I11" t="n">
-        <v>483550</v>
+        <v>479877</v>
       </c>
       <c r="J11" t="n">
-        <v>453213</v>
+        <v>478144</v>
       </c>
       <c r="K11" t="n">
-        <v>996397</v>
+        <v>448686</v>
       </c>
       <c r="L11" t="n">
-        <v>861194</v>
+        <v>995277</v>
       </c>
       <c r="M11" t="n">
-        <v>602085</v>
+        <v>865564</v>
       </c>
       <c r="N11" t="n">
-        <v>578968</v>
+        <v>599775</v>
       </c>
       <c r="O11" t="n">
-        <v>460084</v>
+        <v>638115</v>
       </c>
       <c r="P11" t="n">
-        <v>729839</v>
+        <v>457645</v>
       </c>
       <c r="Q11" t="n">
-        <v>1072349</v>
+        <v>330077</v>
       </c>
       <c r="R11" t="n">
-        <v>546750</v>
+        <v>729337</v>
       </c>
       <c r="S11" t="n">
-        <v>330543</v>
+        <v>1065895</v>
       </c>
       <c r="T11" t="n">
-        <v>5694347</v>
+        <v>542674</v>
       </c>
       <c r="U11" t="n">
-        <v>283371</v>
+        <v>330121</v>
       </c>
       <c r="V11" t="n">
-        <v>1183791</v>
+        <v>281796</v>
       </c>
       <c r="W11" t="n">
-        <v>805980</v>
+        <v>757296</v>
       </c>
       <c r="X11" t="n">
-        <v>1084154</v>
+        <v>258850</v>
       </c>
       <c r="Y11" t="n">
-        <v>331968</v>
+        <v>1220829</v>
       </c>
       <c r="Z11" t="n">
-        <v>758531</v>
+        <v>812086</v>
       </c>
       <c r="AA11" t="n">
-        <v>635567</v>
+        <v>1120246</v>
       </c>
       <c r="AB11" t="n">
-        <v>211792</v>
+        <v>641052</v>
       </c>
       <c r="AC11" t="n">
-        <v>865172</v>
+        <v>210337</v>
       </c>
       <c r="AD11" t="n">
-        <v>895207</v>
+        <v>886546</v>
       </c>
       <c r="AE11" t="n">
-        <v>860549</v>
+        <v>908249</v>
       </c>
       <c r="AF11" t="n">
-        <v>849376</v>
+        <v>481514</v>
       </c>
       <c r="AG11" t="n">
-        <v>476391</v>
+        <v>541756</v>
       </c>
       <c r="AH11" t="n">
-        <v>529912</v>
+        <v>870769</v>
       </c>
       <c r="AI11" t="n">
-        <v>538671</v>
+        <v>562592</v>
       </c>
       <c r="AJ11" t="n">
-        <v>194283</v>
+        <v>193985</v>
       </c>
       <c r="AK11" t="n">
-        <v>698190</v>
+        <v>850285</v>
       </c>
       <c r="AL11" t="n">
-        <v>257939</v>
+        <v>707145</v>
       </c>
       <c r="AM11" t="n">
-        <v>480755</v>
+        <v>533463</v>
       </c>
       <c r="AN11" t="n">
-        <v>554555</v>
+        <v>1496086</v>
       </c>
       <c r="AO11" t="n">
-        <v>1270420</v>
+        <v>486187</v>
       </c>
       <c r="AP11" t="n">
-        <v>529194</v>
+        <v>705729</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1438231</v>
+        <v>560478</v>
       </c>
       <c r="AR11" t="n">
-        <v>681696</v>
+        <v>1302160</v>
       </c>
       <c r="AS11" t="n">
-        <v>227083</v>
+        <v>229542</v>
       </c>
       <c r="AT11" t="n">
-        <v>636666</v>
+        <v>985619</v>
       </c>
       <c r="AU11" t="n">
-        <v>509469</v>
+        <v>1803831</v>
       </c>
       <c r="AV11" t="n">
-        <v>518420</v>
+        <v>963277</v>
       </c>
       <c r="AW11" t="n">
-        <v>1572726</v>
+        <v>1307947</v>
       </c>
       <c r="AX11" t="n">
-        <v>985055</v>
+        <v>422328</v>
       </c>
       <c r="AY11" t="n">
-        <v>347059</v>
+        <v>640734</v>
       </c>
       <c r="AZ11" t="n">
-        <v>714369</v>
+        <v>717451</v>
       </c>
       <c r="BA11" t="n">
-        <v>1140673</v>
+        <v>511188</v>
       </c>
       <c r="BB11" t="n">
-        <v>1794032</v>
+        <v>521125</v>
       </c>
       <c r="BC11" t="n">
-        <v>962592</v>
+        <v>1147710</v>
       </c>
       <c r="BD11" t="n">
-        <v>1308241</v>
+        <v>1580937</v>
       </c>
       <c r="BE11" t="n">
-        <v>1581955</v>
+        <v>1589900</v>
       </c>
       <c r="BF11" t="n">
-        <v>1137651</v>
+        <v>1138778</v>
       </c>
       <c r="BG11" t="n">
-        <v>2624668</v>
+        <v>2635331</v>
       </c>
       <c r="BH11" t="n">
-        <v>1393330</v>
+        <v>1396374</v>
       </c>
       <c r="BI11" t="n">
-        <v>375881</v>
+        <v>377614</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1467006</v>
+        <v>350128</v>
       </c>
       <c r="BK11" t="n">
-        <v>1851049</v>
+        <v>1471185</v>
       </c>
       <c r="BL11" t="n">
-        <v>540197</v>
+        <v>1866299</v>
       </c>
       <c r="BM11" t="n">
-        <v>503203</v>
+        <v>539679</v>
       </c>
       <c r="BN11" t="n">
-        <v>182313</v>
+        <v>508627</v>
       </c>
       <c r="BO11" t="n">
-        <v>1043501</v>
+        <v>467851</v>
       </c>
       <c r="BP11" t="n">
-        <v>1550278</v>
+        <v>1555957</v>
       </c>
       <c r="BQ11" t="n">
-        <v>521570</v>
+        <v>266535</v>
       </c>
       <c r="BR11" t="n">
-        <v>639770</v>
+        <v>398092</v>
       </c>
       <c r="BS11" t="n">
-        <v>459456</v>
+        <v>189777</v>
       </c>
       <c r="BT11" t="n">
-        <v>262721</v>
+        <v>1054247</v>
       </c>
       <c r="BU11" t="n">
-        <v>382485</v>
+        <v>792961</v>
       </c>
       <c r="BV11" t="n">
-        <v>778941</v>
+        <v>705379</v>
       </c>
       <c r="BW11" t="n">
-        <v>690104</v>
+        <v>524291</v>
       </c>
       <c r="BX11" t="n">
-        <v>515025</v>
+        <v>318655</v>
       </c>
       <c r="BY11" t="n">
-        <v>314297</v>
+        <v>1420834</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1405939</v>
+        <v>642377</v>
       </c>
       <c r="CA11" t="n">
-        <v>419607</v>
+        <v>524788</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B12" t="n">
-        <v>66060027</v>
+        <v>66301242</v>
       </c>
       <c r="C12" t="n">
-        <v>1741301</v>
+        <v>5679532</v>
       </c>
       <c r="D12" t="n">
-        <v>1285080</v>
+        <v>1755291</v>
       </c>
       <c r="E12" t="n">
-        <v>747699</v>
+        <v>1289873</v>
       </c>
       <c r="F12" t="n">
-        <v>405959</v>
+        <v>744714</v>
       </c>
       <c r="G12" t="n">
-        <v>277486</v>
+        <v>405936</v>
       </c>
       <c r="H12" t="n">
-        <v>479877</v>
+        <v>280826</v>
       </c>
       <c r="I12" t="n">
-        <v>478144</v>
+        <v>479414</v>
       </c>
       <c r="J12" t="n">
-        <v>448686</v>
+        <v>476157</v>
       </c>
       <c r="K12" t="n">
-        <v>995277</v>
+        <v>446326</v>
       </c>
       <c r="L12" t="n">
-        <v>865564</v>
+        <v>994936</v>
       </c>
       <c r="M12" t="n">
-        <v>599775</v>
+        <v>866129</v>
       </c>
       <c r="N12" t="n">
-        <v>638115</v>
+        <v>598287</v>
       </c>
       <c r="O12" t="n">
-        <v>457645</v>
+        <v>649472</v>
       </c>
       <c r="P12" t="n">
-        <v>729337</v>
+        <v>456247</v>
       </c>
       <c r="Q12" t="n">
-        <v>1065895</v>
+        <v>328993</v>
       </c>
       <c r="R12" t="n">
-        <v>542674</v>
+        <v>728470</v>
       </c>
       <c r="S12" t="n">
-        <v>330121</v>
+        <v>1064649</v>
       </c>
       <c r="T12" t="n">
-        <v>5684531</v>
+        <v>540620</v>
       </c>
       <c r="U12" t="n">
-        <v>281796</v>
+        <v>329688</v>
       </c>
       <c r="V12" t="n">
-        <v>1220829</v>
+        <v>281014</v>
       </c>
       <c r="W12" t="n">
-        <v>812086</v>
+        <v>758003</v>
       </c>
       <c r="X12" t="n">
-        <v>1120246</v>
+        <v>259718</v>
       </c>
       <c r="Y12" t="n">
-        <v>330077</v>
+        <v>1238015</v>
       </c>
       <c r="Z12" t="n">
-        <v>757296</v>
+        <v>815647</v>
       </c>
       <c r="AA12" t="n">
-        <v>641052</v>
+        <v>1137603</v>
       </c>
       <c r="AB12" t="n">
-        <v>210337</v>
+        <v>643531</v>
       </c>
       <c r="AC12" t="n">
-        <v>886546</v>
+        <v>209733</v>
       </c>
       <c r="AD12" t="n">
-        <v>908249</v>
+        <v>890565</v>
       </c>
       <c r="AE12" t="n">
-        <v>870769</v>
+        <v>914273</v>
       </c>
       <c r="AF12" t="n">
-        <v>850285</v>
+        <v>483335</v>
       </c>
       <c r="AG12" t="n">
-        <v>481514</v>
+        <v>546396</v>
       </c>
       <c r="AH12" t="n">
-        <v>541756</v>
+        <v>872615</v>
       </c>
       <c r="AI12" t="n">
-        <v>562592</v>
+        <v>573215</v>
       </c>
       <c r="AJ12" t="n">
-        <v>193985</v>
+        <v>193847</v>
       </c>
       <c r="AK12" t="n">
-        <v>707145</v>
+        <v>850362</v>
       </c>
       <c r="AL12" t="n">
-        <v>258850</v>
+        <v>712449</v>
       </c>
       <c r="AM12" t="n">
-        <v>486187</v>
+        <v>535478</v>
       </c>
       <c r="AN12" t="n">
-        <v>560478</v>
+        <v>1522285</v>
       </c>
       <c r="AO12" t="n">
-        <v>1302160</v>
+        <v>489592</v>
       </c>
       <c r="AP12" t="n">
-        <v>533463</v>
+        <v>717276</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1496086</v>
+        <v>563014</v>
       </c>
       <c r="AR12" t="n">
-        <v>705729</v>
+        <v>1318687</v>
       </c>
       <c r="AS12" t="n">
-        <v>229542</v>
+        <v>229782</v>
       </c>
       <c r="AT12" t="n">
-        <v>640734</v>
+        <v>985676</v>
       </c>
       <c r="AU12" t="n">
-        <v>511188</v>
+        <v>1805903</v>
       </c>
       <c r="AV12" t="n">
-        <v>521125</v>
+        <v>963060</v>
       </c>
       <c r="AW12" t="n">
-        <v>1580937</v>
+        <v>1307560</v>
       </c>
       <c r="AX12" t="n">
-        <v>985619</v>
+        <v>423485</v>
       </c>
       <c r="AY12" t="n">
-        <v>350128</v>
+        <v>642220</v>
       </c>
       <c r="AZ12" t="n">
-        <v>717451</v>
+        <v>718406</v>
       </c>
       <c r="BA12" t="n">
-        <v>1147710</v>
+        <v>511878</v>
       </c>
       <c r="BB12" t="n">
-        <v>1803831</v>
+        <v>521995</v>
       </c>
       <c r="BC12" t="n">
-        <v>963277</v>
+        <v>1150876</v>
       </c>
       <c r="BD12" t="n">
-        <v>1307947</v>
+        <v>1584878</v>
       </c>
       <c r="BE12" t="n">
-        <v>1589900</v>
+        <v>1593378</v>
       </c>
       <c r="BF12" t="n">
-        <v>1138778</v>
+        <v>1139067</v>
       </c>
       <c r="BG12" t="n">
-        <v>2635331</v>
+        <v>2642815</v>
       </c>
       <c r="BH12" t="n">
-        <v>1396374</v>
+        <v>1397519</v>
       </c>
       <c r="BI12" t="n">
-        <v>377614</v>
+        <v>378363</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1471185</v>
+        <v>351532</v>
       </c>
       <c r="BK12" t="n">
-        <v>1866299</v>
+        <v>1472521</v>
       </c>
       <c r="BL12" t="n">
-        <v>539679</v>
+        <v>1872091</v>
       </c>
       <c r="BM12" t="n">
-        <v>508627</v>
+        <v>539136</v>
       </c>
       <c r="BN12" t="n">
-        <v>189777</v>
+        <v>510307</v>
       </c>
       <c r="BO12" t="n">
-        <v>1054247</v>
+        <v>471754</v>
       </c>
       <c r="BP12" t="n">
-        <v>1555957</v>
+        <v>1558958</v>
       </c>
       <c r="BQ12" t="n">
-        <v>524291</v>
+        <v>267866</v>
       </c>
       <c r="BR12" t="n">
-        <v>642377</v>
+        <v>406113</v>
       </c>
       <c r="BS12" t="n">
-        <v>467851</v>
+        <v>191134</v>
       </c>
       <c r="BT12" t="n">
-        <v>266535</v>
+        <v>1060541</v>
       </c>
       <c r="BU12" t="n">
-        <v>398092</v>
+        <v>799357</v>
       </c>
       <c r="BV12" t="n">
-        <v>792961</v>
+        <v>713937</v>
       </c>
       <c r="BW12" t="n">
-        <v>705379</v>
+        <v>524951</v>
       </c>
       <c r="BX12" t="n">
-        <v>524788</v>
+        <v>320637</v>
       </c>
       <c r="BY12" t="n">
-        <v>318655</v>
+        <v>1428429</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1420834</v>
+        <v>643093</v>
       </c>
       <c r="CA12" t="n">
-        <v>422328</v>
+        <v>529811</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B13" t="n">
-        <v>66301242</v>
+        <v>66486458</v>
       </c>
       <c r="C13" t="n">
-        <v>1755291</v>
+        <v>5671457</v>
       </c>
       <c r="D13" t="n">
-        <v>1289873</v>
+        <v>1771499</v>
       </c>
       <c r="E13" t="n">
-        <v>744714</v>
+        <v>1295217</v>
       </c>
       <c r="F13" t="n">
-        <v>405936</v>
+        <v>740600</v>
       </c>
       <c r="G13" t="n">
-        <v>280826</v>
+        <v>405515</v>
       </c>
       <c r="H13" t="n">
-        <v>479414</v>
+        <v>283352</v>
       </c>
       <c r="I13" t="n">
-        <v>476157</v>
+        <v>478608</v>
       </c>
       <c r="J13" t="n">
-        <v>446326</v>
+        <v>473786</v>
       </c>
       <c r="K13" t="n">
-        <v>994936</v>
+        <v>443408</v>
       </c>
       <c r="L13" t="n">
-        <v>866129</v>
+        <v>993496</v>
       </c>
       <c r="M13" t="n">
-        <v>598287</v>
+        <v>866068</v>
       </c>
       <c r="N13" t="n">
-        <v>649472</v>
+        <v>596165</v>
       </c>
       <c r="O13" t="n">
-        <v>456247</v>
+        <v>660147</v>
       </c>
       <c r="P13" t="n">
-        <v>728470</v>
+        <v>454252</v>
       </c>
       <c r="Q13" t="n">
-        <v>1064649</v>
+        <v>327437</v>
       </c>
       <c r="R13" t="n">
-        <v>540620</v>
+        <v>726836</v>
       </c>
       <c r="S13" t="n">
-        <v>329688</v>
+        <v>1061926</v>
       </c>
       <c r="T13" t="n">
-        <v>5679532</v>
+        <v>537843</v>
       </c>
       <c r="U13" t="n">
-        <v>281014</v>
+        <v>329026</v>
       </c>
       <c r="V13" t="n">
-        <v>1238015</v>
+        <v>280246</v>
       </c>
       <c r="W13" t="n">
-        <v>815647</v>
+        <v>757145</v>
       </c>
       <c r="X13" t="n">
-        <v>1137603</v>
+        <v>260421</v>
       </c>
       <c r="Y13" t="n">
-        <v>328993</v>
+        <v>1255840</v>
       </c>
       <c r="Z13" t="n">
-        <v>758003</v>
+        <v>818815</v>
       </c>
       <c r="AA13" t="n">
-        <v>643531</v>
+        <v>1154848</v>
       </c>
       <c r="AB13" t="n">
-        <v>209733</v>
+        <v>645468</v>
       </c>
       <c r="AC13" t="n">
-        <v>890565</v>
+        <v>208912</v>
       </c>
       <c r="AD13" t="n">
-        <v>914273</v>
+        <v>894338</v>
       </c>
       <c r="AE13" t="n">
-        <v>872615</v>
+        <v>918542</v>
       </c>
       <c r="AF13" t="n">
-        <v>850362</v>
+        <v>484743</v>
       </c>
       <c r="AG13" t="n">
-        <v>483335</v>
+        <v>551466</v>
       </c>
       <c r="AH13" t="n">
-        <v>546396</v>
+        <v>873310</v>
       </c>
       <c r="AI13" t="n">
-        <v>573215</v>
+        <v>581334</v>
       </c>
       <c r="AJ13" t="n">
-        <v>193847</v>
+        <v>193548</v>
       </c>
       <c r="AK13" t="n">
-        <v>712449</v>
+        <v>847526</v>
       </c>
       <c r="AL13" t="n">
-        <v>259718</v>
+        <v>717561</v>
       </c>
       <c r="AM13" t="n">
-        <v>489592</v>
+        <v>537097</v>
       </c>
       <c r="AN13" t="n">
-        <v>563014</v>
+        <v>1546873</v>
       </c>
       <c r="AO13" t="n">
-        <v>1318687</v>
+        <v>493159</v>
       </c>
       <c r="AP13" t="n">
-        <v>535478</v>
+        <v>729035</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1522285</v>
+        <v>565198</v>
       </c>
       <c r="AR13" t="n">
-        <v>717276</v>
+        <v>1335742</v>
       </c>
       <c r="AS13" t="n">
-        <v>229782</v>
+        <v>229936</v>
       </c>
       <c r="AT13" t="n">
-        <v>642220</v>
+        <v>984381</v>
       </c>
       <c r="AU13" t="n">
-        <v>511878</v>
+        <v>1804384</v>
       </c>
       <c r="AV13" t="n">
-        <v>521995</v>
+        <v>962856</v>
       </c>
       <c r="AW13" t="n">
-        <v>1584878</v>
+        <v>1306210</v>
       </c>
       <c r="AX13" t="n">
-        <v>985676</v>
+        <v>424016</v>
       </c>
       <c r="AY13" t="n">
-        <v>351532</v>
+        <v>642862</v>
       </c>
       <c r="AZ13" t="n">
-        <v>718406</v>
+        <v>718961</v>
       </c>
       <c r="BA13" t="n">
-        <v>1150876</v>
+        <v>512449</v>
       </c>
       <c r="BB13" t="n">
-        <v>1805903</v>
+        <v>522207</v>
       </c>
       <c r="BC13" t="n">
-        <v>963060</v>
+        <v>1152835</v>
       </c>
       <c r="BD13" t="n">
-        <v>1307560</v>
+        <v>1586656</v>
       </c>
       <c r="BE13" t="n">
-        <v>1593378</v>
+        <v>1595299</v>
       </c>
       <c r="BF13" t="n">
-        <v>1139067</v>
+        <v>1138067</v>
       </c>
       <c r="BG13" t="n">
-        <v>2642815</v>
+        <v>2647663</v>
       </c>
       <c r="BH13" t="n">
-        <v>1397519</v>
+        <v>1397343</v>
       </c>
       <c r="BI13" t="n">
-        <v>378363</v>
+        <v>378530</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1472521</v>
+        <v>352727</v>
       </c>
       <c r="BK13" t="n">
-        <v>1872091</v>
+        <v>1472934</v>
       </c>
       <c r="BL13" t="n">
-        <v>539136</v>
+        <v>1876347</v>
       </c>
       <c r="BM13" t="n">
-        <v>510307</v>
+        <v>538013</v>
       </c>
       <c r="BN13" t="n">
-        <v>191134</v>
+        <v>511134</v>
       </c>
       <c r="BO13" t="n">
-        <v>1060541</v>
+        <v>475239</v>
       </c>
       <c r="BP13" t="n">
-        <v>1558958</v>
+        <v>1561179</v>
       </c>
       <c r="BQ13" t="n">
-        <v>524951</v>
+        <v>268513</v>
       </c>
       <c r="BR13" t="n">
-        <v>643093</v>
+        <v>413397</v>
       </c>
       <c r="BS13" t="n">
-        <v>471754</v>
+        <v>192619</v>
       </c>
       <c r="BT13" t="n">
-        <v>267866</v>
+        <v>1065756</v>
       </c>
       <c r="BU13" t="n">
-        <v>406113</v>
+        <v>805248</v>
       </c>
       <c r="BV13" t="n">
-        <v>799357</v>
+        <v>721591</v>
       </c>
       <c r="BW13" t="n">
-        <v>713937</v>
+        <v>524955</v>
       </c>
       <c r="BX13" t="n">
-        <v>529811</v>
+        <v>322580</v>
       </c>
       <c r="BY13" t="n">
-        <v>320637</v>
+        <v>1434298</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1428429</v>
+        <v>643140</v>
       </c>
       <c r="CA13" t="n">
-        <v>423485</v>
+        <v>534328</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B14" t="n">
-        <v>66486458</v>
+        <v>66372831</v>
       </c>
       <c r="C14" t="n">
-        <v>1771499</v>
+        <v>5627243</v>
       </c>
       <c r="D14" t="n">
-        <v>1295217</v>
+        <v>1781812</v>
       </c>
       <c r="E14" t="n">
-        <v>740600</v>
+        <v>1296664</v>
       </c>
       <c r="F14" t="n">
-        <v>405515</v>
+        <v>733640</v>
       </c>
       <c r="G14" t="n">
-        <v>283352</v>
+        <v>403542</v>
       </c>
       <c r="H14" t="n">
-        <v>478608</v>
+        <v>284343</v>
       </c>
       <c r="I14" t="n">
-        <v>473786</v>
+        <v>477476</v>
       </c>
       <c r="J14" t="n">
-        <v>443408</v>
+        <v>469856</v>
       </c>
       <c r="K14" t="n">
-        <v>993496</v>
+        <v>439537</v>
       </c>
       <c r="L14" t="n">
-        <v>866068</v>
+        <v>987196</v>
       </c>
       <c r="M14" t="n">
-        <v>596165</v>
+        <v>857364</v>
       </c>
       <c r="N14" t="n">
-        <v>660147</v>
+        <v>591477</v>
       </c>
       <c r="O14" t="n">
-        <v>454252</v>
+        <v>667942</v>
       </c>
       <c r="P14" t="n">
-        <v>726836</v>
+        <v>450923</v>
       </c>
       <c r="Q14" t="n">
-        <v>1061926</v>
+        <v>324544</v>
       </c>
       <c r="R14" t="n">
-        <v>537843</v>
+        <v>719993</v>
       </c>
       <c r="S14" t="n">
-        <v>329026</v>
+        <v>1050098</v>
       </c>
       <c r="T14" t="n">
-        <v>5671457</v>
+        <v>534311</v>
       </c>
       <c r="U14" t="n">
-        <v>280246</v>
+        <v>327243</v>
       </c>
       <c r="V14" t="n">
-        <v>1255840</v>
+        <v>278119</v>
       </c>
       <c r="W14" t="n">
-        <v>818815</v>
+        <v>749242</v>
       </c>
       <c r="X14" t="n">
-        <v>1154848</v>
+        <v>260416</v>
       </c>
       <c r="Y14" t="n">
-        <v>327437</v>
+        <v>1271065</v>
       </c>
       <c r="Z14" t="n">
-        <v>757145</v>
+        <v>819638</v>
       </c>
       <c r="AA14" t="n">
-        <v>645468</v>
+        <v>1170008</v>
       </c>
       <c r="AB14" t="n">
-        <v>208912</v>
+        <v>644869</v>
       </c>
       <c r="AC14" t="n">
-        <v>894338</v>
+        <v>207172</v>
       </c>
       <c r="AD14" t="n">
-        <v>918542</v>
+        <v>893751</v>
       </c>
       <c r="AE14" t="n">
-        <v>873310</v>
+        <v>920380</v>
       </c>
       <c r="AF14" t="n">
-        <v>847526</v>
+        <v>483692</v>
       </c>
       <c r="AG14" t="n">
-        <v>484743</v>
+        <v>552398</v>
       </c>
       <c r="AH14" t="n">
-        <v>551466</v>
+        <v>871207</v>
       </c>
       <c r="AI14" t="n">
-        <v>581334</v>
+        <v>585451</v>
       </c>
       <c r="AJ14" t="n">
-        <v>193548</v>
+        <v>192678</v>
       </c>
       <c r="AK14" t="n">
-        <v>717561</v>
+        <v>842481</v>
       </c>
       <c r="AL14" t="n">
-        <v>260421</v>
+        <v>720416</v>
       </c>
       <c r="AM14" t="n">
-        <v>493159</v>
+        <v>536629</v>
       </c>
       <c r="AN14" t="n">
-        <v>565198</v>
+        <v>1562593</v>
       </c>
       <c r="AO14" t="n">
-        <v>1335742</v>
+        <v>494175</v>
       </c>
       <c r="AP14" t="n">
-        <v>537097</v>
+        <v>738139</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1546873</v>
+        <v>563614</v>
       </c>
       <c r="AR14" t="n">
-        <v>729035</v>
+        <v>1348177</v>
       </c>
       <c r="AS14" t="n">
-        <v>229936</v>
+        <v>229247</v>
       </c>
       <c r="AT14" t="n">
-        <v>642862</v>
+        <v>980297</v>
       </c>
       <c r="AU14" t="n">
-        <v>512449</v>
+        <v>1798702</v>
       </c>
       <c r="AV14" t="n">
-        <v>522207</v>
+        <v>958163</v>
       </c>
       <c r="AW14" t="n">
-        <v>1586656</v>
+        <v>1301926</v>
       </c>
       <c r="AX14" t="n">
-        <v>984381</v>
+        <v>423067</v>
       </c>
       <c r="AY14" t="n">
-        <v>352727</v>
+        <v>640843</v>
       </c>
       <c r="AZ14" t="n">
-        <v>718961</v>
+        <v>718169</v>
       </c>
       <c r="BA14" t="n">
-        <v>1152835</v>
+        <v>511125</v>
       </c>
       <c r="BB14" t="n">
-        <v>1804384</v>
+        <v>519873</v>
       </c>
       <c r="BC14" t="n">
-        <v>962856</v>
+        <v>1150164</v>
       </c>
       <c r="BD14" t="n">
-        <v>1306210</v>
+        <v>1577315</v>
       </c>
       <c r="BE14" t="n">
-        <v>1595299</v>
+        <v>1588466</v>
       </c>
       <c r="BF14" t="n">
-        <v>1138067</v>
+        <v>1131140</v>
       </c>
       <c r="BG14" t="n">
-        <v>2647663</v>
+        <v>2641067</v>
       </c>
       <c r="BH14" t="n">
-        <v>1397343</v>
+        <v>1387526</v>
       </c>
       <c r="BI14" t="n">
-        <v>378530</v>
+        <v>377317</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1472934</v>
+        <v>352043</v>
       </c>
       <c r="BK14" t="n">
-        <v>1876347</v>
+        <v>1465719</v>
       </c>
       <c r="BL14" t="n">
-        <v>538013</v>
+        <v>1872422</v>
       </c>
       <c r="BM14" t="n">
-        <v>511134</v>
+        <v>535900</v>
       </c>
       <c r="BN14" t="n">
-        <v>192619</v>
+        <v>510256</v>
       </c>
       <c r="BO14" t="n">
-        <v>1065756</v>
+        <v>477254</v>
       </c>
       <c r="BP14" t="n">
-        <v>1561179</v>
+        <v>1556325</v>
       </c>
       <c r="BQ14" t="n">
-        <v>524955</v>
+        <v>268509</v>
       </c>
       <c r="BR14" t="n">
-        <v>643140</v>
+        <v>415527</v>
       </c>
       <c r="BS14" t="n">
-        <v>475239</v>
+        <v>193871</v>
       </c>
       <c r="BT14" t="n">
-        <v>268513</v>
+        <v>1067867</v>
       </c>
       <c r="BU14" t="n">
-        <v>413397</v>
+        <v>806224</v>
       </c>
       <c r="BV14" t="n">
-        <v>805248</v>
+        <v>725559</v>
       </c>
       <c r="BW14" t="n">
-        <v>721591</v>
+        <v>523971</v>
       </c>
       <c r="BX14" t="n">
-        <v>534328</v>
+        <v>323841</v>
       </c>
       <c r="BY14" t="n">
-        <v>322580</v>
+        <v>1432288</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1434298</v>
+        <v>641868</v>
       </c>
       <c r="CA14" t="n">
-        <v>424016</v>
+        <v>537466</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B15" t="n">
-        <v>66372831</v>
+        <v>66179083</v>
       </c>
       <c r="C15" t="n">
-        <v>1781812</v>
+        <v>5558108</v>
       </c>
       <c r="D15" t="n">
-        <v>1296664</v>
+        <v>1786877</v>
       </c>
       <c r="E15" t="n">
-        <v>733640</v>
+        <v>1296725</v>
       </c>
       <c r="F15" t="n">
-        <v>403542</v>
+        <v>726821</v>
       </c>
       <c r="G15" t="n">
-        <v>284343</v>
+        <v>401574</v>
       </c>
       <c r="H15" t="n">
-        <v>477476</v>
+        <v>285232</v>
       </c>
       <c r="I15" t="n">
-        <v>469856</v>
+        <v>476300</v>
       </c>
       <c r="J15" t="n">
-        <v>439537</v>
+        <v>465930</v>
       </c>
       <c r="K15" t="n">
-        <v>987196</v>
+        <v>435965</v>
       </c>
       <c r="L15" t="n">
-        <v>857364</v>
+        <v>980156</v>
       </c>
       <c r="M15" t="n">
-        <v>591477</v>
+        <v>848432</v>
       </c>
       <c r="N15" t="n">
-        <v>667942</v>
+        <v>586617</v>
       </c>
       <c r="O15" t="n">
-        <v>450923</v>
+        <v>673423</v>
       </c>
       <c r="P15" t="n">
-        <v>719993</v>
+        <v>447446</v>
       </c>
       <c r="Q15" t="n">
-        <v>1050098</v>
+        <v>321454</v>
       </c>
       <c r="R15" t="n">
-        <v>534311</v>
+        <v>713130</v>
       </c>
       <c r="S15" t="n">
-        <v>327243</v>
+        <v>1037668</v>
       </c>
       <c r="T15" t="n">
-        <v>5627243</v>
+        <v>530852</v>
       </c>
       <c r="U15" t="n">
-        <v>278119</v>
+        <v>325492</v>
       </c>
       <c r="V15" t="n">
-        <v>1271065</v>
+        <v>275673</v>
       </c>
       <c r="W15" t="n">
-        <v>819638</v>
+        <v>741200</v>
       </c>
       <c r="X15" t="n">
-        <v>1170008</v>
+        <v>260256</v>
       </c>
       <c r="Y15" t="n">
-        <v>324544</v>
+        <v>1282690</v>
       </c>
       <c r="Z15" t="n">
-        <v>749242</v>
+        <v>819799</v>
       </c>
       <c r="AA15" t="n">
-        <v>644869</v>
+        <v>1183235</v>
       </c>
       <c r="AB15" t="n">
-        <v>207172</v>
+        <v>643895</v>
       </c>
       <c r="AC15" t="n">
-        <v>893751</v>
+        <v>205211</v>
       </c>
       <c r="AD15" t="n">
-        <v>920380</v>
+        <v>893014</v>
       </c>
       <c r="AE15" t="n">
-        <v>871207</v>
+        <v>921450</v>
       </c>
       <c r="AF15" t="n">
-        <v>842481</v>
+        <v>482534</v>
       </c>
       <c r="AG15" t="n">
-        <v>483692</v>
+        <v>551924</v>
       </c>
       <c r="AH15" t="n">
-        <v>552398</v>
+        <v>868797</v>
       </c>
       <c r="AI15" t="n">
-        <v>585451</v>
+        <v>586494</v>
       </c>
       <c r="AJ15" t="n">
-        <v>192678</v>
+        <v>191447</v>
       </c>
       <c r="AK15" t="n">
-        <v>720416</v>
+        <v>836993</v>
       </c>
       <c r="AL15" t="n">
-        <v>260416</v>
+        <v>722448</v>
       </c>
       <c r="AM15" t="n">
-        <v>494175</v>
+        <v>536058</v>
       </c>
       <c r="AN15" t="n">
-        <v>563614</v>
+        <v>1575278</v>
       </c>
       <c r="AO15" t="n">
-        <v>1348177</v>
+        <v>494498</v>
       </c>
       <c r="AP15" t="n">
-        <v>536629</v>
+        <v>746433</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1562593</v>
+        <v>561459</v>
       </c>
       <c r="AR15" t="n">
-        <v>738139</v>
+        <v>1353964</v>
       </c>
       <c r="AS15" t="n">
-        <v>229247</v>
+        <v>228456</v>
       </c>
       <c r="AT15" t="n">
-        <v>640843</v>
+        <v>976373</v>
       </c>
       <c r="AU15" t="n">
-        <v>511125</v>
+        <v>1792697</v>
       </c>
       <c r="AV15" t="n">
-        <v>519873</v>
+        <v>950985</v>
       </c>
       <c r="AW15" t="n">
-        <v>1577315</v>
+        <v>1297326</v>
       </c>
       <c r="AX15" t="n">
-        <v>980297</v>
+        <v>422019</v>
       </c>
       <c r="AY15" t="n">
-        <v>352043</v>
+        <v>638734</v>
       </c>
       <c r="AZ15" t="n">
-        <v>718169</v>
+        <v>717121</v>
       </c>
       <c r="BA15" t="n">
-        <v>1150164</v>
+        <v>509236</v>
       </c>
       <c r="BB15" t="n">
-        <v>1798702</v>
+        <v>517140</v>
       </c>
       <c r="BC15" t="n">
-        <v>958163</v>
+        <v>1146612</v>
       </c>
       <c r="BD15" t="n">
-        <v>1301926</v>
+        <v>1567247</v>
       </c>
       <c r="BE15" t="n">
-        <v>1588466</v>
+        <v>1580495</v>
       </c>
       <c r="BF15" t="n">
-        <v>1131140</v>
+        <v>1123595</v>
       </c>
       <c r="BG15" t="n">
-        <v>2641067</v>
+        <v>2633681</v>
       </c>
       <c r="BH15" t="n">
-        <v>1387526</v>
+        <v>1377226</v>
       </c>
       <c r="BI15" t="n">
-        <v>377317</v>
+        <v>376273</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1465719</v>
+        <v>351198</v>
       </c>
       <c r="BK15" t="n">
-        <v>1872422</v>
+        <v>1458068</v>
       </c>
       <c r="BL15" t="n">
-        <v>535900</v>
+        <v>1867608</v>
       </c>
       <c r="BM15" t="n">
-        <v>510256</v>
+        <v>533948</v>
       </c>
       <c r="BN15" t="n">
-        <v>193871</v>
+        <v>509344</v>
       </c>
       <c r="BO15" t="n">
-        <v>1067867</v>
+        <v>478561</v>
       </c>
       <c r="BP15" t="n">
-        <v>1556325</v>
+        <v>1550033</v>
       </c>
       <c r="BQ15" t="n">
-        <v>523971</v>
+        <v>268123</v>
       </c>
       <c r="BR15" t="n">
-        <v>641868</v>
+        <v>416629</v>
       </c>
       <c r="BS15" t="n">
-        <v>477254</v>
+        <v>194473</v>
       </c>
       <c r="BT15" t="n">
-        <v>268509</v>
+        <v>1070096</v>
       </c>
       <c r="BU15" t="n">
-        <v>415527</v>
+        <v>807045</v>
       </c>
       <c r="BV15" t="n">
-        <v>806224</v>
+        <v>727799</v>
       </c>
       <c r="BW15" t="n">
-        <v>725559</v>
+        <v>522810</v>
       </c>
       <c r="BX15" t="n">
-        <v>537466</v>
+        <v>324467</v>
       </c>
       <c r="BY15" t="n">
-        <v>323841</v>
+        <v>1430073</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1432288</v>
+        <v>640182</v>
       </c>
       <c r="CA15" t="n">
-        <v>423067</v>
+        <v>540458</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B16" t="n">
-        <v>66179083</v>
+        <v>66171439</v>
       </c>
       <c r="C16" t="n">
-        <v>1786877</v>
+        <v>5527994</v>
       </c>
       <c r="D16" t="n">
-        <v>1296725</v>
+        <v>1789385</v>
       </c>
       <c r="E16" t="n">
-        <v>726821</v>
+        <v>1298425</v>
       </c>
       <c r="F16" t="n">
-        <v>401574</v>
+        <v>724678</v>
       </c>
       <c r="G16" t="n">
-        <v>285232</v>
+        <v>401139</v>
       </c>
       <c r="H16" t="n">
-        <v>476300</v>
+        <v>285916</v>
       </c>
       <c r="I16" t="n">
-        <v>465930</v>
+        <v>475875</v>
       </c>
       <c r="J16" t="n">
-        <v>435965</v>
+        <v>464505</v>
       </c>
       <c r="K16" t="n">
-        <v>980156</v>
+        <v>434580</v>
       </c>
       <c r="L16" t="n">
-        <v>848432</v>
+        <v>978372</v>
       </c>
       <c r="M16" t="n">
-        <v>586617</v>
+        <v>847384</v>
       </c>
       <c r="N16" t="n">
-        <v>673423</v>
+        <v>585352</v>
       </c>
       <c r="O16" t="n">
-        <v>447446</v>
+        <v>676583</v>
       </c>
       <c r="P16" t="n">
-        <v>713130</v>
+        <v>446148</v>
       </c>
       <c r="Q16" t="n">
-        <v>1037668</v>
+        <v>320432</v>
       </c>
       <c r="R16" t="n">
-        <v>530852</v>
+        <v>712143</v>
       </c>
       <c r="S16" t="n">
-        <v>325492</v>
+        <v>1035028</v>
       </c>
       <c r="T16" t="n">
-        <v>5558108</v>
+        <v>529395</v>
       </c>
       <c r="U16" t="n">
-        <v>275673</v>
+        <v>325116</v>
       </c>
       <c r="V16" t="n">
-        <v>1282690</v>
+        <v>274763</v>
       </c>
       <c r="W16" t="n">
-        <v>819799</v>
+        <v>739473</v>
       </c>
       <c r="X16" t="n">
-        <v>1183235</v>
+        <v>260433</v>
       </c>
       <c r="Y16" t="n">
-        <v>321454</v>
+        <v>1288637</v>
       </c>
       <c r="Z16" t="n">
-        <v>741200</v>
+        <v>820512</v>
       </c>
       <c r="AA16" t="n">
-        <v>643895</v>
+        <v>1190060</v>
       </c>
       <c r="AB16" t="n">
-        <v>205211</v>
+        <v>643963</v>
       </c>
       <c r="AC16" t="n">
-        <v>893014</v>
+        <v>204526</v>
       </c>
       <c r="AD16" t="n">
-        <v>921450</v>
+        <v>894054</v>
       </c>
       <c r="AE16" t="n">
-        <v>868797</v>
+        <v>922171</v>
       </c>
       <c r="AF16" t="n">
-        <v>836993</v>
+        <v>482875</v>
       </c>
       <c r="AG16" t="n">
-        <v>482534</v>
+        <v>553171</v>
       </c>
       <c r="AH16" t="n">
-        <v>551924</v>
+        <v>868281</v>
       </c>
       <c r="AI16" t="n">
-        <v>586494</v>
+        <v>586789</v>
       </c>
       <c r="AJ16" t="n">
-        <v>191447</v>
+        <v>190842</v>
       </c>
       <c r="AK16" t="n">
-        <v>722448</v>
+        <v>835360</v>
       </c>
       <c r="AL16" t="n">
-        <v>260256</v>
+        <v>724178</v>
       </c>
       <c r="AM16" t="n">
-        <v>494498</v>
+        <v>536557</v>
       </c>
       <c r="AN16" t="n">
-        <v>561459</v>
+        <v>1583672</v>
       </c>
       <c r="AO16" t="n">
-        <v>1353964</v>
+        <v>495325</v>
       </c>
       <c r="AP16" t="n">
-        <v>536058</v>
+        <v>751343</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1575278</v>
+        <v>561992</v>
       </c>
       <c r="AR16" t="n">
-        <v>746433</v>
+        <v>1356449</v>
       </c>
       <c r="AS16" t="n">
-        <v>228456</v>
+        <v>228376</v>
       </c>
       <c r="AT16" t="n">
-        <v>638734</v>
+        <v>975570</v>
       </c>
       <c r="AU16" t="n">
-        <v>509236</v>
+        <v>1790863</v>
       </c>
       <c r="AV16" t="n">
-        <v>517140</v>
+        <v>948310</v>
       </c>
       <c r="AW16" t="n">
-        <v>1567247</v>
+        <v>1296013</v>
       </c>
       <c r="AX16" t="n">
-        <v>976373</v>
+        <v>421995</v>
       </c>
       <c r="AY16" t="n">
-        <v>351198</v>
+        <v>638732</v>
       </c>
       <c r="AZ16" t="n">
-        <v>717121</v>
+        <v>717040</v>
       </c>
       <c r="BA16" t="n">
-        <v>1146612</v>
+        <v>509001</v>
       </c>
       <c r="BB16" t="n">
-        <v>1792697</v>
+        <v>516843</v>
       </c>
       <c r="BC16" t="n">
-        <v>950985</v>
+        <v>1146286</v>
       </c>
       <c r="BD16" t="n">
-        <v>1297326</v>
+        <v>1566510</v>
       </c>
       <c r="BE16" t="n">
-        <v>1580495</v>
+        <v>1579805</v>
       </c>
       <c r="BF16" t="n">
-        <v>1123595</v>
+        <v>1122265</v>
       </c>
       <c r="BG16" t="n">
-        <v>2633681</v>
+        <v>2634154</v>
       </c>
       <c r="BH16" t="n">
-        <v>1377226</v>
+        <v>1376230</v>
       </c>
       <c r="BI16" t="n">
-        <v>376273</v>
+        <v>376350</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1458068</v>
+        <v>351484</v>
       </c>
       <c r="BK16" t="n">
-        <v>1867608</v>
+        <v>1457556</v>
       </c>
       <c r="BL16" t="n">
-        <v>533948</v>
+        <v>1868519</v>
       </c>
       <c r="BM16" t="n">
-        <v>509344</v>
+        <v>533394</v>
       </c>
       <c r="BN16" t="n">
-        <v>194473</v>
+        <v>509479</v>
       </c>
       <c r="BO16" t="n">
-        <v>1070096</v>
+        <v>479351</v>
       </c>
       <c r="BP16" t="n">
-        <v>1550033</v>
+        <v>1549344</v>
       </c>
       <c r="BQ16" t="n">
-        <v>522810</v>
+        <v>268016</v>
       </c>
       <c r="BR16" t="n">
-        <v>640182</v>
+        <v>418785</v>
       </c>
       <c r="BS16" t="n">
-        <v>478561</v>
+        <v>194573</v>
       </c>
       <c r="BT16" t="n">
-        <v>268123</v>
+        <v>1072464</v>
       </c>
       <c r="BU16" t="n">
-        <v>416629</v>
+        <v>809660</v>
       </c>
       <c r="BV16" t="n">
-        <v>807045</v>
+        <v>729581</v>
       </c>
       <c r="BW16" t="n">
-        <v>727799</v>
+        <v>522541</v>
       </c>
       <c r="BX16" t="n">
-        <v>540458</v>
+        <v>324835</v>
       </c>
       <c r="BY16" t="n">
-        <v>324467</v>
+        <v>1431536</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1430073</v>
+        <v>639788</v>
       </c>
       <c r="CA16" t="n">
-        <v>422019</v>
+        <v>542314</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B17" t="n">
-        <v>66171439</v>
+        <v>66130957</v>
       </c>
       <c r="C17" t="n">
-        <v>1789385</v>
+        <v>5511463</v>
       </c>
       <c r="D17" t="n">
-        <v>1298425</v>
+        <v>1790929</v>
       </c>
       <c r="E17" t="n">
-        <v>724678</v>
+        <v>1299030</v>
       </c>
       <c r="F17" t="n">
-        <v>401139</v>
+        <v>721734</v>
       </c>
       <c r="G17" t="n">
-        <v>285916</v>
+        <v>400348</v>
       </c>
       <c r="H17" t="n">
-        <v>475875</v>
+        <v>286350</v>
       </c>
       <c r="I17" t="n">
-        <v>464505</v>
+        <v>475207</v>
       </c>
       <c r="J17" t="n">
-        <v>434580</v>
+        <v>462968</v>
       </c>
       <c r="K17" t="n">
-        <v>978372</v>
+        <v>432624</v>
       </c>
       <c r="L17" t="n">
-        <v>847384</v>
+        <v>975879</v>
       </c>
       <c r="M17" t="n">
-        <v>585352</v>
+        <v>845938</v>
       </c>
       <c r="N17" t="n">
-        <v>676583</v>
+        <v>583502</v>
       </c>
       <c r="O17" t="n">
-        <v>446148</v>
+        <v>680361</v>
       </c>
       <c r="P17" t="n">
-        <v>712143</v>
+        <v>444548</v>
       </c>
       <c r="Q17" t="n">
-        <v>1035028</v>
+        <v>319370</v>
       </c>
       <c r="R17" t="n">
-        <v>529395</v>
+        <v>710458</v>
       </c>
       <c r="S17" t="n">
-        <v>325116</v>
+        <v>1031921</v>
       </c>
       <c r="T17" t="n">
-        <v>5527994</v>
+        <v>527669</v>
       </c>
       <c r="U17" t="n">
-        <v>274763</v>
+        <v>324487</v>
       </c>
       <c r="V17" t="n">
-        <v>1288637</v>
+        <v>273675</v>
       </c>
       <c r="W17" t="n">
-        <v>820512</v>
+        <v>737382</v>
       </c>
       <c r="X17" t="n">
-        <v>1190060</v>
+        <v>260419</v>
       </c>
       <c r="Y17" t="n">
-        <v>320432</v>
+        <v>1292276</v>
       </c>
       <c r="Z17" t="n">
-        <v>739473</v>
+        <v>820464</v>
       </c>
       <c r="AA17" t="n">
-        <v>643963</v>
+        <v>1195796</v>
       </c>
       <c r="AB17" t="n">
-        <v>204526</v>
+        <v>641272</v>
       </c>
       <c r="AC17" t="n">
-        <v>894054</v>
+        <v>203661</v>
       </c>
       <c r="AD17" t="n">
-        <v>922171</v>
+        <v>894168</v>
       </c>
       <c r="AE17" t="n">
-        <v>868281</v>
+        <v>922026</v>
       </c>
       <c r="AF17" t="n">
-        <v>835360</v>
+        <v>482912</v>
       </c>
       <c r="AG17" t="n">
-        <v>482875</v>
+        <v>553234</v>
       </c>
       <c r="AH17" t="n">
-        <v>553171</v>
+        <v>867043</v>
       </c>
       <c r="AI17" t="n">
-        <v>586789</v>
+        <v>588108</v>
       </c>
       <c r="AJ17" t="n">
-        <v>190842</v>
+        <v>190147</v>
       </c>
       <c r="AK17" t="n">
-        <v>724178</v>
+        <v>833027</v>
       </c>
       <c r="AL17" t="n">
-        <v>260433</v>
+        <v>725433</v>
       </c>
       <c r="AM17" t="n">
-        <v>495325</v>
+        <v>536351</v>
       </c>
       <c r="AN17" t="n">
-        <v>561992</v>
+        <v>1589214</v>
       </c>
       <c r="AO17" t="n">
-        <v>1356449</v>
+        <v>496551</v>
       </c>
       <c r="AP17" t="n">
-        <v>536557</v>
+        <v>755364</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1583672</v>
+        <v>562404</v>
       </c>
       <c r="AR17" t="n">
-        <v>751343</v>
+        <v>1358338</v>
       </c>
       <c r="AS17" t="n">
-        <v>228376</v>
+        <v>228092</v>
       </c>
       <c r="AT17" t="n">
-        <v>638732</v>
+        <v>973835</v>
       </c>
       <c r="AU17" t="n">
-        <v>509001</v>
+        <v>1787752</v>
       </c>
       <c r="AV17" t="n">
-        <v>516843</v>
+        <v>946457</v>
       </c>
       <c r="AW17" t="n">
-        <v>1566510</v>
+        <v>1293572</v>
       </c>
       <c r="AX17" t="n">
-        <v>975570</v>
+        <v>421840</v>
       </c>
       <c r="AY17" t="n">
-        <v>351484</v>
+        <v>638037</v>
       </c>
       <c r="AZ17" t="n">
-        <v>717040</v>
+        <v>716844</v>
       </c>
       <c r="BA17" t="n">
-        <v>1146286</v>
+        <v>508664</v>
       </c>
       <c r="BB17" t="n">
-        <v>1790863</v>
+        <v>516320</v>
       </c>
       <c r="BC17" t="n">
-        <v>948310</v>
+        <v>1145737</v>
       </c>
       <c r="BD17" t="n">
-        <v>1296013</v>
+        <v>1564780</v>
       </c>
       <c r="BE17" t="n">
-        <v>1579805</v>
+        <v>1578361</v>
       </c>
       <c r="BF17" t="n">
-        <v>1122265</v>
+        <v>1120095</v>
       </c>
       <c r="BG17" t="n">
-        <v>2634154</v>
+        <v>2632106</v>
       </c>
       <c r="BH17" t="n">
-        <v>1376230</v>
+        <v>1374571</v>
       </c>
       <c r="BI17" t="n">
-        <v>376350</v>
+        <v>375866</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1457556</v>
+        <v>351537</v>
       </c>
       <c r="BK17" t="n">
-        <v>1868519</v>
+        <v>1456144</v>
       </c>
       <c r="BL17" t="n">
-        <v>533394</v>
+        <v>1869163</v>
       </c>
       <c r="BM17" t="n">
-        <v>509479</v>
+        <v>532497</v>
       </c>
       <c r="BN17" t="n">
-        <v>194573</v>
+        <v>509433</v>
       </c>
       <c r="BO17" t="n">
-        <v>1072464</v>
+        <v>479705</v>
       </c>
       <c r="BP17" t="n">
-        <v>1549344</v>
+        <v>1547246</v>
       </c>
       <c r="BQ17" t="n">
-        <v>522541</v>
+        <v>267729</v>
       </c>
       <c r="BR17" t="n">
-        <v>639788</v>
+        <v>418339</v>
       </c>
       <c r="BS17" t="n">
-        <v>479351</v>
+        <v>194400</v>
       </c>
       <c r="BT17" t="n">
-        <v>268016</v>
+        <v>1073064</v>
       </c>
       <c r="BU17" t="n">
-        <v>418785</v>
+        <v>811891</v>
       </c>
       <c r="BV17" t="n">
-        <v>809660</v>
+        <v>731269</v>
       </c>
       <c r="BW17" t="n">
-        <v>729581</v>
+        <v>522080</v>
       </c>
       <c r="BX17" t="n">
-        <v>542314</v>
+        <v>325069</v>
       </c>
       <c r="BY17" t="n">
-        <v>324835</v>
+        <v>1431300</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1431536</v>
+        <v>638997</v>
       </c>
       <c r="CA17" t="n">
-        <v>421995</v>
+        <v>544114</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B18" t="n">
-        <v>66130957</v>
+        <v>66071545</v>
       </c>
       <c r="C18" t="n">
-        <v>1790929</v>
+        <v>5483259</v>
       </c>
       <c r="D18" t="n">
-        <v>1299030</v>
+        <v>1794774</v>
       </c>
       <c r="E18" t="n">
-        <v>721734</v>
+        <v>1299306</v>
       </c>
       <c r="F18" t="n">
-        <v>400348</v>
+        <v>715133</v>
       </c>
       <c r="G18" t="n">
-        <v>286350</v>
+        <v>398998</v>
       </c>
       <c r="H18" t="n">
-        <v>475207</v>
+        <v>287215</v>
       </c>
       <c r="I18" t="n">
-        <v>462968</v>
+        <v>473630</v>
       </c>
       <c r="J18" t="n">
-        <v>432624</v>
+        <v>459858</v>
       </c>
       <c r="K18" t="n">
-        <v>975879</v>
+        <v>428499</v>
       </c>
       <c r="L18" t="n">
-        <v>845938</v>
+        <v>970403</v>
       </c>
       <c r="M18" t="n">
-        <v>583502</v>
+        <v>843111</v>
       </c>
       <c r="N18" t="n">
-        <v>680361</v>
+        <v>579759</v>
       </c>
       <c r="O18" t="n">
-        <v>444548</v>
+        <v>687927</v>
       </c>
       <c r="P18" t="n">
-        <v>710458</v>
+        <v>441289</v>
       </c>
       <c r="Q18" t="n">
-        <v>1031921</v>
+        <v>317263</v>
       </c>
       <c r="R18" t="n">
-        <v>527669</v>
+        <v>706861</v>
       </c>
       <c r="S18" t="n">
-        <v>324487</v>
+        <v>1025348</v>
       </c>
       <c r="T18" t="n">
-        <v>5511463</v>
+        <v>523925</v>
       </c>
       <c r="U18" t="n">
-        <v>273675</v>
+        <v>323066</v>
       </c>
       <c r="V18" t="n">
-        <v>1292276</v>
+        <v>271656</v>
       </c>
       <c r="W18" t="n">
-        <v>820464</v>
+        <v>732495</v>
       </c>
       <c r="X18" t="n">
-        <v>1195796</v>
+        <v>260261</v>
       </c>
       <c r="Y18" t="n">
-        <v>319370</v>
+        <v>1302004</v>
       </c>
       <c r="Z18" t="n">
-        <v>737382</v>
+        <v>821261</v>
       </c>
       <c r="AA18" t="n">
-        <v>641272</v>
+        <v>1210365</v>
       </c>
       <c r="AB18" t="n">
-        <v>203661</v>
+        <v>638704</v>
       </c>
       <c r="AC18" t="n">
-        <v>894168</v>
+        <v>202117</v>
       </c>
       <c r="AD18" t="n">
-        <v>922026</v>
+        <v>894781</v>
       </c>
       <c r="AE18" t="n">
-        <v>867043</v>
+        <v>923201</v>
       </c>
       <c r="AF18" t="n">
-        <v>833027</v>
+        <v>483305</v>
       </c>
       <c r="AG18" t="n">
-        <v>482912</v>
+        <v>552137</v>
       </c>
       <c r="AH18" t="n">
-        <v>553234</v>
+        <v>865276</v>
       </c>
       <c r="AI18" t="n">
-        <v>588108</v>
+        <v>590730</v>
       </c>
       <c r="AJ18" t="n">
-        <v>190147</v>
+        <v>188723</v>
       </c>
       <c r="AK18" t="n">
-        <v>725433</v>
+        <v>828542</v>
       </c>
       <c r="AL18" t="n">
-        <v>260419</v>
+        <v>728615</v>
       </c>
       <c r="AM18" t="n">
-        <v>496551</v>
+        <v>536290</v>
       </c>
       <c r="AN18" t="n">
-        <v>562404</v>
+        <v>1606412</v>
       </c>
       <c r="AO18" t="n">
-        <v>1358338</v>
+        <v>498671</v>
       </c>
       <c r="AP18" t="n">
-        <v>536351</v>
+        <v>765287</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1589214</v>
+        <v>562860</v>
       </c>
       <c r="AR18" t="n">
-        <v>755364</v>
+        <v>1366598</v>
       </c>
       <c r="AS18" t="n">
-        <v>228092</v>
+        <v>227430</v>
       </c>
       <c r="AT18" t="n">
-        <v>638037</v>
+        <v>970084</v>
       </c>
       <c r="AU18" t="n">
-        <v>508664</v>
+        <v>1782008</v>
       </c>
       <c r="AV18" t="n">
-        <v>516320</v>
+        <v>941261</v>
       </c>
       <c r="AW18" t="n">
-        <v>1564780</v>
+        <v>1287984</v>
       </c>
       <c r="AX18" t="n">
-        <v>973835</v>
+        <v>421086</v>
       </c>
       <c r="AY18" t="n">
-        <v>351537</v>
+        <v>636242</v>
       </c>
       <c r="AZ18" t="n">
-        <v>716844</v>
+        <v>715466</v>
       </c>
       <c r="BA18" t="n">
-        <v>1145737</v>
+        <v>507599</v>
       </c>
       <c r="BB18" t="n">
-        <v>1787752</v>
+        <v>514909</v>
       </c>
       <c r="BC18" t="n">
-        <v>946457</v>
+        <v>1143922</v>
       </c>
       <c r="BD18" t="n">
-        <v>1293572</v>
+        <v>1560788</v>
       </c>
       <c r="BE18" t="n">
-        <v>1578361</v>
+        <v>1575073</v>
       </c>
       <c r="BF18" t="n">
-        <v>1120095</v>
+        <v>1115652</v>
       </c>
       <c r="BG18" t="n">
-        <v>2632106</v>
+        <v>2627927</v>
       </c>
       <c r="BH18" t="n">
-        <v>1374571</v>
+        <v>1370376</v>
       </c>
       <c r="BI18" t="n">
-        <v>375866</v>
+        <v>374760</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1456144</v>
+        <v>351592</v>
       </c>
       <c r="BK18" t="n">
-        <v>1869163</v>
+        <v>1452532</v>
       </c>
       <c r="BL18" t="n">
-        <v>532497</v>
+        <v>1869708</v>
       </c>
       <c r="BM18" t="n">
-        <v>509433</v>
+        <v>530239</v>
       </c>
       <c r="BN18" t="n">
-        <v>194400</v>
+        <v>509122</v>
       </c>
       <c r="BO18" t="n">
-        <v>1073064</v>
+        <v>481089</v>
       </c>
       <c r="BP18" t="n">
-        <v>1547246</v>
+        <v>1543051</v>
       </c>
       <c r="BQ18" t="n">
-        <v>522080</v>
+        <v>267250</v>
       </c>
       <c r="BR18" t="n">
-        <v>638997</v>
+        <v>420746</v>
       </c>
       <c r="BS18" t="n">
-        <v>479705</v>
+        <v>193799</v>
       </c>
       <c r="BT18" t="n">
-        <v>267729</v>
+        <v>1074726</v>
       </c>
       <c r="BU18" t="n">
-        <v>418339</v>
+        <v>816642</v>
       </c>
       <c r="BV18" t="n">
-        <v>811891</v>
+        <v>735017</v>
       </c>
       <c r="BW18" t="n">
-        <v>731269</v>
+        <v>521109</v>
       </c>
       <c r="BX18" t="n">
-        <v>544114</v>
+        <v>325387</v>
       </c>
       <c r="BY18" t="n">
-        <v>325069</v>
+        <v>1431512</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1431300</v>
+        <v>637612</v>
       </c>
       <c r="CA18" t="n">
-        <v>421840</v>
+        <v>547930</v>
       </c>
     </row>
   </sheetData>
